--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133202459</v>
+        <v>133202423</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623775</v>
+        <v>623825</v>
       </c>
       <c r="R4" t="n">
-        <v>6941872</v>
+        <v>6941925</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,45 +1006,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202438</v>
+        <v>133202450</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623820</v>
+        <v>623712</v>
       </c>
       <c r="R5" t="n">
-        <v>6942117</v>
+        <v>6941985</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1094,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,48 +1126,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202423</v>
+        <v>133202461</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623825</v>
+        <v>623727</v>
       </c>
       <c r="R6" t="n">
-        <v>6941925</v>
+        <v>6941870</v>
       </c>
       <c r="S6" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1214,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,53 +1246,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202461</v>
+        <v>133202459</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623727</v>
+        <v>623775</v>
       </c>
       <c r="R7" t="n">
-        <v>6941870</v>
+        <v>6941872</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,53 +1358,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202450</v>
+        <v>133202438</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623712</v>
+        <v>623820</v>
       </c>
       <c r="R8" t="n">
-        <v>6941985</v>
+        <v>6942117</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2023,7 +2023,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133202426</v>
+        <v>133202443</v>
       </c>
       <c r="B14" t="n">
         <v>99130</v>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623801</v>
+        <v>623768</v>
       </c>
       <c r="R14" t="n">
-        <v>6941940</v>
+        <v>6942054</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,32 +2135,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133202443</v>
+        <v>133202424</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623768</v>
+        <v>623813</v>
       </c>
       <c r="R15" t="n">
-        <v>6942054</v>
+        <v>6941951</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,12 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,32 +2242,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133202424</v>
+        <v>133202426</v>
       </c>
       <c r="B16" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623813</v>
+        <v>623801</v>
       </c>
       <c r="R16" t="n">
-        <v>6941951</v>
+        <v>6941940</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2327,7 +2322,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2792,10 +2792,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133202432</v>
+        <v>133202458</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,34 +2803,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623820</v>
+        <v>623770</v>
       </c>
       <c r="R21" t="n">
-        <v>6942033</v>
+        <v>6941875</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2862,7 +2870,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2872,7 +2880,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,45 +2912,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133202460</v>
+        <v>133202464</v>
       </c>
       <c r="B22" t="n">
-        <v>92290</v>
+        <v>57958</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623768</v>
+        <v>623782</v>
       </c>
       <c r="R22" t="n">
-        <v>6941880</v>
+        <v>6941914</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2969,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +3000,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,53 +3032,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133202464</v>
+        <v>133202460</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>92290</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623782</v>
+        <v>623768</v>
       </c>
       <c r="R23" t="n">
-        <v>6941914</v>
+        <v>6941880</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3084,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3094,12 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3126,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133202458</v>
+        <v>133202432</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,42 +3150,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623770</v>
+        <v>623820</v>
       </c>
       <c r="R24" t="n">
-        <v>6941875</v>
+        <v>6942033</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3204,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3214,12 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4045,10 +4045,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133202437</v>
+        <v>133202440</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,42 +4056,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623840</v>
+        <v>623827</v>
       </c>
       <c r="R32" t="n">
-        <v>6942067</v>
+        <v>6942150</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4123,7 +4115,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4133,12 +4125,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,10 +4152,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133202440</v>
+        <v>133202437</v>
       </c>
       <c r="B33" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4176,34 +4163,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623827</v>
+        <v>623840</v>
       </c>
       <c r="R33" t="n">
-        <v>6942150</v>
+        <v>6942067</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4235,7 +4230,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4245,7 +4240,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4272,7 +4272,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133202435</v>
+        <v>133202445</v>
       </c>
       <c r="B34" t="n">
         <v>57958</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623795</v>
+        <v>623745</v>
       </c>
       <c r="R34" t="n">
-        <v>6942074</v>
+        <v>6942050</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4392,7 +4392,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133202445</v>
+        <v>133202435</v>
       </c>
       <c r="B35" t="n">
         <v>57958</v>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623745</v>
+        <v>623795</v>
       </c>
       <c r="R35" t="n">
-        <v>6942050</v>
+        <v>6942074</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4619,32 +4619,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133202430</v>
+        <v>133202434</v>
       </c>
       <c r="B37" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623819</v>
+        <v>623790</v>
       </c>
       <c r="R37" t="n">
-        <v>6942027</v>
+        <v>6942049</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,7 +4699,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,32 +4731,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133202431</v>
+        <v>133202430</v>
       </c>
       <c r="B38" t="n">
-        <v>80467</v>
+        <v>80438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4764,7 +4769,7 @@
         <v>623819</v>
       </c>
       <c r="R38" t="n">
-        <v>6942029</v>
+        <v>6942027</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4796,7 +4801,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4806,7 +4811,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4833,32 +4838,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133202434</v>
+        <v>133202431</v>
       </c>
       <c r="B39" t="n">
-        <v>99130</v>
+        <v>80467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4868,10 +4873,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623790</v>
+        <v>623819</v>
       </c>
       <c r="R39" t="n">
-        <v>6942049</v>
+        <v>6942029</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4903,7 +4908,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4913,12 +4918,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5276,32 +5276,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133240773</v>
+        <v>133240755</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623688</v>
+        <v>623822</v>
       </c>
       <c r="R43" t="n">
-        <v>6941982</v>
+        <v>6941942</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>27 ex</t>
+          <t>Spillning ( färskt)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,32 +5388,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133240755</v>
+        <v>133240773</v>
       </c>
       <c r="B44" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623822</v>
+        <v>623688</v>
       </c>
       <c r="R44" t="n">
-        <v>6941942</v>
+        <v>6941982</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Spillning ( färskt)</t>
+          <t>27 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5714,10 +5714,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133240763</v>
+        <v>133240766</v>
       </c>
       <c r="B47" t="n">
-        <v>92378</v>
+        <v>92566</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>483</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5749,13 +5749,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623739</v>
+        <v>623736</v>
       </c>
       <c r="R47" t="n">
-        <v>6942054</v>
+        <v>6942055</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5821,10 +5821,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133240766</v>
+        <v>133240763</v>
       </c>
       <c r="B48" t="n">
-        <v>92566</v>
+        <v>92378</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623736</v>
+        <v>623739</v>
       </c>
       <c r="R48" t="n">
-        <v>6942055</v>
+        <v>6942054</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7038,7 +7038,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133240759</v>
+        <v>133240777</v>
       </c>
       <c r="B59" t="n">
         <v>99130</v>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>623852</v>
+        <v>623724</v>
       </c>
       <c r="R59" t="n">
-        <v>6942122</v>
+        <v>6941914</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7150,7 +7150,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133240777</v>
+        <v>133240759</v>
       </c>
       <c r="B60" t="n">
         <v>99130</v>
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>623724</v>
+        <v>623852</v>
       </c>
       <c r="R60" t="n">
-        <v>6941914</v>
+        <v>6942122</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133202425</v>
+        <v>133202433</v>
       </c>
       <c r="B2" t="n">
         <v>99130</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623809</v>
+        <v>623817</v>
       </c>
       <c r="R2" t="n">
-        <v>6941943</v>
+        <v>6942024</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133202433</v>
+        <v>133202425</v>
       </c>
       <c r="B3" t="n">
         <v>99130</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623817</v>
+        <v>623809</v>
       </c>
       <c r="R3" t="n">
-        <v>6942024</v>
+        <v>6941943</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1006,53 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202450</v>
+        <v>133202459</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623712</v>
+        <v>623775</v>
       </c>
       <c r="R5" t="n">
-        <v>6941985</v>
+        <v>6941872</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,12 +1086,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,53 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202461</v>
+        <v>133202438</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623727</v>
+        <v>623820</v>
       </c>
       <c r="R6" t="n">
-        <v>6941870</v>
+        <v>6942117</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,12 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,45 +1230,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202459</v>
+        <v>133202461</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623775</v>
+        <v>623727</v>
       </c>
       <c r="R7" t="n">
-        <v>6941872</v>
+        <v>6941870</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1318,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,45 +1350,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202438</v>
+        <v>133202450</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623820</v>
+        <v>623712</v>
       </c>
       <c r="R8" t="n">
-        <v>6942117</v>
+        <v>6941985</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2023,32 +2023,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133202443</v>
+        <v>133202424</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623768</v>
+        <v>623813</v>
       </c>
       <c r="R14" t="n">
-        <v>6942054</v>
+        <v>6941951</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,12 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,32 +2130,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133202424</v>
+        <v>133202426</v>
       </c>
       <c r="B15" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623813</v>
+        <v>623801</v>
       </c>
       <c r="R15" t="n">
-        <v>6941951</v>
+        <v>6941940</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2205,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2210,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,7 +2242,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133202426</v>
+        <v>133202443</v>
       </c>
       <c r="B16" t="n">
         <v>99130</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623801</v>
+        <v>623768</v>
       </c>
       <c r="R16" t="n">
-        <v>6941940</v>
+        <v>6942054</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2685,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133202454</v>
+        <v>133202464</v>
       </c>
       <c r="B20" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,34 +2696,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623773</v>
+        <v>623782</v>
       </c>
       <c r="R20" t="n">
-        <v>6941893</v>
+        <v>6941914</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2755,7 +2763,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2765,7 +2773,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2912,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133202464</v>
+        <v>133202454</v>
       </c>
       <c r="B22" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,42 +2936,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623782</v>
+        <v>623773</v>
       </c>
       <c r="R22" t="n">
-        <v>6941914</v>
+        <v>6941893</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2990,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,12 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,32 +3032,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133202460</v>
+        <v>133202432</v>
       </c>
       <c r="B23" t="n">
-        <v>92290</v>
+        <v>91918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623768</v>
+        <v>623820</v>
       </c>
       <c r="R23" t="n">
-        <v>6941880</v>
+        <v>6942033</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,32 +3139,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133202432</v>
+        <v>133202460</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>92290</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623820</v>
+        <v>623768</v>
       </c>
       <c r="R24" t="n">
-        <v>6942033</v>
+        <v>6941880</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,10 +3246,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133202441</v>
+        <v>133202444</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>92338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3257,42 +3257,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623776</v>
+        <v>623743</v>
       </c>
       <c r="R25" t="n">
-        <v>6942117</v>
+        <v>6942053</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3324,7 +3316,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3326,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,6 +3335,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3478,10 +3466,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133202444</v>
+        <v>133202441</v>
       </c>
       <c r="B27" t="n">
-        <v>92338</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,34 +3477,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623743</v>
+        <v>623776</v>
       </c>
       <c r="R27" t="n">
-        <v>6942053</v>
+        <v>6942117</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3548,7 +3544,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3558,7 +3554,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3567,7 +3568,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133202463</v>
+        <v>133202448</v>
       </c>
       <c r="B29" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3709,34 +3709,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623712</v>
+        <v>623750</v>
       </c>
       <c r="R29" t="n">
-        <v>6941856</v>
+        <v>6941932</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3768,7 +3776,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3778,7 +3786,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3805,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133202448</v>
+        <v>133202463</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3816,42 +3829,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623750</v>
+        <v>623712</v>
       </c>
       <c r="R30" t="n">
-        <v>6941932</v>
+        <v>6941856</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3883,7 +3888,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3893,12 +3898,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4272,7 +4272,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133202445</v>
+        <v>133202435</v>
       </c>
       <c r="B34" t="n">
         <v>57958</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623745</v>
+        <v>623795</v>
       </c>
       <c r="R34" t="n">
-        <v>6942050</v>
+        <v>6942074</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4392,7 +4392,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133202435</v>
+        <v>133202445</v>
       </c>
       <c r="B35" t="n">
         <v>57958</v>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623795</v>
+        <v>623745</v>
       </c>
       <c r="R35" t="n">
-        <v>6942074</v>
+        <v>6942050</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4619,32 +4619,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133202434</v>
+        <v>133202430</v>
       </c>
       <c r="B37" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623790</v>
+        <v>623819</v>
       </c>
       <c r="R37" t="n">
-        <v>6942049</v>
+        <v>6942027</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,12 +4699,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4731,32 +4726,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133202430</v>
+        <v>133202431</v>
       </c>
       <c r="B38" t="n">
-        <v>80438</v>
+        <v>80467</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4769,7 +4764,7 @@
         <v>623819</v>
       </c>
       <c r="R38" t="n">
-        <v>6942027</v>
+        <v>6942029</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4801,7 +4796,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4811,7 +4806,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,32 +4833,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133202431</v>
+        <v>133202434</v>
       </c>
       <c r="B39" t="n">
-        <v>80467</v>
+        <v>99130</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4873,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623819</v>
+        <v>623790</v>
       </c>
       <c r="R39" t="n">
-        <v>6942029</v>
+        <v>6942049</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4908,7 +4903,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4918,7 +4913,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5276,32 +5276,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133240755</v>
+        <v>133240773</v>
       </c>
       <c r="B43" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623822</v>
+        <v>623688</v>
       </c>
       <c r="R43" t="n">
-        <v>6941942</v>
+        <v>6941982</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Spillning ( färskt)</t>
+          <t>27 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,32 +5388,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133240773</v>
+        <v>133240755</v>
       </c>
       <c r="B44" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623688</v>
+        <v>623822</v>
       </c>
       <c r="R44" t="n">
-        <v>6941982</v>
+        <v>6941942</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>27 ex</t>
+          <t>Spillning ( färskt)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5928,32 +5928,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133240772</v>
+        <v>133240771</v>
       </c>
       <c r="B49" t="n">
-        <v>91932</v>
+        <v>99130</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623681</v>
+        <v>623737</v>
       </c>
       <c r="R49" t="n">
-        <v>6942020</v>
+        <v>6942012</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6008,7 +6008,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6142,32 +6147,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133240771</v>
+        <v>133240772</v>
       </c>
       <c r="B51" t="n">
-        <v>99130</v>
+        <v>91932</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6177,10 +6182,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623737</v>
+        <v>623681</v>
       </c>
       <c r="R51" t="n">
-        <v>6942012</v>
+        <v>6942020</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6212,7 +6217,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6222,12 +6227,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6478,7 +6478,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133240758</v>
+        <v>133240764</v>
       </c>
       <c r="B54" t="n">
         <v>99130</v>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>623824</v>
+        <v>623736</v>
       </c>
       <c r="R54" t="n">
-        <v>6941997</v>
+        <v>6942051</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6590,7 +6590,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133240764</v>
+        <v>133240758</v>
       </c>
       <c r="B55" t="n">
         <v>99130</v>
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>623736</v>
+        <v>623824</v>
       </c>
       <c r="R55" t="n">
-        <v>6942051</v>
+        <v>6941997</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6702,7 +6702,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133240776</v>
+        <v>133240761</v>
       </c>
       <c r="B56" t="n">
         <v>99130</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>623720</v>
+        <v>623740</v>
       </c>
       <c r="R56" t="n">
-        <v>6941939</v>
+        <v>6942057</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>18 sex</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6814,7 +6814,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133240761</v>
+        <v>133240776</v>
       </c>
       <c r="B57" t="n">
         <v>99130</v>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>623740</v>
+        <v>623720</v>
       </c>
       <c r="R57" t="n">
-        <v>6942057</v>
+        <v>6941939</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>18 sex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7038,7 +7038,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133240777</v>
+        <v>133240759</v>
       </c>
       <c r="B59" t="n">
         <v>99130</v>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>623724</v>
+        <v>623852</v>
       </c>
       <c r="R59" t="n">
-        <v>6941914</v>
+        <v>6942122</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7150,7 +7150,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133240759</v>
+        <v>133240777</v>
       </c>
       <c r="B60" t="n">
         <v>99130</v>
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>623852</v>
+        <v>623724</v>
       </c>
       <c r="R60" t="n">
-        <v>6942122</v>
+        <v>6941914</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133202433</v>
+        <v>133202425</v>
       </c>
       <c r="B2" t="n">
         <v>99130</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623817</v>
+        <v>623809</v>
       </c>
       <c r="R2" t="n">
-        <v>6942024</v>
+        <v>6941943</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133202425</v>
+        <v>133202433</v>
       </c>
       <c r="B3" t="n">
         <v>99130</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623809</v>
+        <v>623817</v>
       </c>
       <c r="R3" t="n">
-        <v>6941943</v>
+        <v>6942024</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,48 +899,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133202423</v>
+        <v>133202450</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623825</v>
+        <v>623712</v>
       </c>
       <c r="R4" t="n">
-        <v>6941925</v>
+        <v>6941985</v>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +987,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +1019,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202459</v>
+        <v>133202461</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623775</v>
+        <v>623727</v>
       </c>
       <c r="R5" t="n">
-        <v>6941872</v>
+        <v>6941870</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1107,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1230,56 +1251,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202461</v>
+        <v>133202423</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623727</v>
+        <v>623825</v>
       </c>
       <c r="R7" t="n">
-        <v>6941870</v>
+        <v>6941925</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,12 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,53 +1358,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202450</v>
+        <v>133202459</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623712</v>
+        <v>623775</v>
       </c>
       <c r="R8" t="n">
-        <v>6941985</v>
+        <v>6941872</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1809,32 +1809,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133202429</v>
+        <v>133202424</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623803</v>
+        <v>623813</v>
       </c>
       <c r="R12" t="n">
-        <v>6942012</v>
+        <v>6941951</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133202436</v>
+        <v>133202426</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623821</v>
+        <v>623801</v>
       </c>
       <c r="R13" t="n">
-        <v>6942067</v>
+        <v>6941940</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133202424</v>
+        <v>133202443</v>
       </c>
       <c r="B14" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2058,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623813</v>
+        <v>623768</v>
       </c>
       <c r="R14" t="n">
-        <v>6941951</v>
+        <v>6942054</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2093,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2108,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,32 +2140,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133202426</v>
+        <v>133202436</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623801</v>
+        <v>623821</v>
       </c>
       <c r="R15" t="n">
-        <v>6941940</v>
+        <v>6942067</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2200,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,12 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>25 ex</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,32 +2247,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133202443</v>
+        <v>133202429</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2282,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623768</v>
+        <v>623803</v>
       </c>
       <c r="R16" t="n">
-        <v>6942054</v>
+        <v>6942012</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2312,7 +2317,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,12 +2327,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,32 +2354,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133202452</v>
+        <v>133202453</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2389,13 +2389,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623775</v>
+        <v>623773</v>
       </c>
       <c r="R17" t="n">
-        <v>6941903</v>
+        <v>6941896</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2434,7 +2434,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2461,7 +2466,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133202453</v>
+        <v>133202442</v>
       </c>
       <c r="B18" t="n">
         <v>99130</v>
@@ -2496,13 +2501,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623773</v>
+        <v>623770</v>
       </c>
       <c r="R18" t="n">
-        <v>6941896</v>
+        <v>6942069</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2531,7 +2536,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2541,12 +2546,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,32 +2578,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133202442</v>
+        <v>133202452</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623770</v>
+        <v>623775</v>
       </c>
       <c r="R19" t="n">
-        <v>6942069</v>
+        <v>6941903</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2643,7 +2648,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,12 +2658,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3032,32 +3032,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133202432</v>
+        <v>133202460</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>92290</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623820</v>
+        <v>623768</v>
       </c>
       <c r="R23" t="n">
-        <v>6942033</v>
+        <v>6941880</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,32 +3139,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133202460</v>
+        <v>133202432</v>
       </c>
       <c r="B24" t="n">
-        <v>92290</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623768</v>
+        <v>623820</v>
       </c>
       <c r="R24" t="n">
-        <v>6941880</v>
+        <v>6942033</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3354,48 +3354,56 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133202455</v>
+        <v>133202441</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623779</v>
+        <v>623776</v>
       </c>
       <c r="R26" t="n">
-        <v>6941893</v>
+        <v>6942117</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3424,7 +3432,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3434,12 +3442,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>300+ ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3466,56 +3474,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133202441</v>
+        <v>133202455</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623776</v>
+        <v>623779</v>
       </c>
       <c r="R27" t="n">
-        <v>6942117</v>
+        <v>6941893</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>300+ ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4272,7 +4272,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133202435</v>
+        <v>133202445</v>
       </c>
       <c r="B34" t="n">
         <v>57958</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623795</v>
+        <v>623745</v>
       </c>
       <c r="R34" t="n">
-        <v>6942074</v>
+        <v>6942050</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4392,7 +4392,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133202445</v>
+        <v>133202435</v>
       </c>
       <c r="B35" t="n">
         <v>57958</v>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623745</v>
+        <v>623795</v>
       </c>
       <c r="R35" t="n">
-        <v>6942050</v>
+        <v>6942074</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4619,32 +4619,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133202430</v>
+        <v>133202431</v>
       </c>
       <c r="B37" t="n">
-        <v>80438</v>
+        <v>80467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4657,7 +4657,7 @@
         <v>623819</v>
       </c>
       <c r="R37" t="n">
-        <v>6942027</v>
+        <v>6942029</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,32 +4726,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133202431</v>
+        <v>133202430</v>
       </c>
       <c r="B38" t="n">
-        <v>80467</v>
+        <v>80438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4764,7 +4764,7 @@
         <v>623819</v>
       </c>
       <c r="R38" t="n">
-        <v>6942029</v>
+        <v>6942027</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5276,32 +5276,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133240773</v>
+        <v>133240755</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623688</v>
+        <v>623822</v>
       </c>
       <c r="R43" t="n">
-        <v>6941982</v>
+        <v>6941942</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>27 ex</t>
+          <t>Spillning ( färskt)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,32 +5388,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133240755</v>
+        <v>133240773</v>
       </c>
       <c r="B44" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623822</v>
+        <v>623688</v>
       </c>
       <c r="R44" t="n">
-        <v>6941942</v>
+        <v>6941982</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Spillning ( färskt)</t>
+          <t>27 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5714,10 +5714,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133240766</v>
+        <v>133240763</v>
       </c>
       <c r="B47" t="n">
-        <v>92566</v>
+        <v>92378</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>483</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5749,13 +5749,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623736</v>
+        <v>623739</v>
       </c>
       <c r="R47" t="n">
-        <v>6942055</v>
+        <v>6942054</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5821,10 +5821,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133240763</v>
+        <v>133240766</v>
       </c>
       <c r="B48" t="n">
-        <v>92378</v>
+        <v>92566</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>483</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623739</v>
+        <v>623736</v>
       </c>
       <c r="R48" t="n">
-        <v>6942054</v>
+        <v>6942055</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5928,32 +5928,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133240771</v>
+        <v>133240760</v>
       </c>
       <c r="B49" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623737</v>
+        <v>623830</v>
       </c>
       <c r="R49" t="n">
-        <v>6942012</v>
+        <v>6942141</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6008,12 +6008,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6040,10 +6035,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133240760</v>
+        <v>133240772</v>
       </c>
       <c r="B50" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6051,21 +6046,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623830</v>
+        <v>623681</v>
       </c>
       <c r="R50" t="n">
-        <v>6942141</v>
+        <v>6942020</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6110,7 +6105,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6120,7 +6115,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6147,32 +6142,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133240772</v>
+        <v>133240771</v>
       </c>
       <c r="B51" t="n">
-        <v>91932</v>
+        <v>99130</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6182,10 +6177,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623681</v>
+        <v>623737</v>
       </c>
       <c r="R51" t="n">
-        <v>6942020</v>
+        <v>6942012</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6217,7 +6212,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6227,7 +6222,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6366,7 +6366,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133240767</v>
+        <v>133240758</v>
       </c>
       <c r="B53" t="n">
         <v>99130</v>
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>623753</v>
+        <v>623824</v>
       </c>
       <c r="R53" t="n">
-        <v>6942055</v>
+        <v>6941997</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>57 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6478,7 +6478,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133240764</v>
+        <v>133240767</v>
       </c>
       <c r="B54" t="n">
         <v>99130</v>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>623736</v>
+        <v>623753</v>
       </c>
       <c r="R54" t="n">
-        <v>6942051</v>
+        <v>6942055</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>57 ex</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6590,7 +6590,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133240758</v>
+        <v>133240764</v>
       </c>
       <c r="B55" t="n">
         <v>99130</v>
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>623824</v>
+        <v>623736</v>
       </c>
       <c r="R55" t="n">
-        <v>6941997</v>
+        <v>6942051</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6702,7 +6702,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133240761</v>
+        <v>133240776</v>
       </c>
       <c r="B56" t="n">
         <v>99130</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>623740</v>
+        <v>623720</v>
       </c>
       <c r="R56" t="n">
-        <v>6942057</v>
+        <v>6941939</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>18 sex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6814,7 +6814,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133240776</v>
+        <v>133240761</v>
       </c>
       <c r="B57" t="n">
         <v>99130</v>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>623720</v>
+        <v>623740</v>
       </c>
       <c r="R57" t="n">
-        <v>6941939</v>
+        <v>6942057</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>18 sex</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133202425</v>
+        <v>133202433</v>
       </c>
       <c r="B2" t="n">
         <v>99130</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623809</v>
+        <v>623817</v>
       </c>
       <c r="R2" t="n">
-        <v>6941943</v>
+        <v>6942024</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133202433</v>
+        <v>133202425</v>
       </c>
       <c r="B3" t="n">
         <v>99130</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623817</v>
+        <v>623809</v>
       </c>
       <c r="R3" t="n">
-        <v>6942024</v>
+        <v>6941943</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,56 +899,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133202450</v>
+        <v>133202423</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623712</v>
+        <v>623825</v>
       </c>
       <c r="R4" t="n">
-        <v>6941985</v>
+        <v>6941925</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202461</v>
+        <v>133202450</v>
       </c>
       <c r="B5" t="n">
         <v>57958</v>
@@ -1062,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623727</v>
+        <v>623712</v>
       </c>
       <c r="R5" t="n">
-        <v>6941870</v>
+        <v>6941985</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,12 +1094,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,45 +1126,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202438</v>
+        <v>133202461</v>
       </c>
       <c r="B6" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623820</v>
+        <v>623727</v>
       </c>
       <c r="R6" t="n">
-        <v>6942117</v>
+        <v>6941870</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,12 +1214,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,32 +1246,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202423</v>
+        <v>133202459</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,13 +1281,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623825</v>
+        <v>623775</v>
       </c>
       <c r="R7" t="n">
-        <v>6941925</v>
+        <v>6941872</v>
       </c>
       <c r="S7" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202459</v>
+        <v>133202438</v>
       </c>
       <c r="B8" t="n">
         <v>99130</v>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623775</v>
+        <v>623820</v>
       </c>
       <c r="R8" t="n">
-        <v>6941872</v>
+        <v>6942117</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1582,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133202427</v>
+        <v>133202465</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,34 +1593,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623760</v>
+        <v>623786</v>
       </c>
       <c r="R10" t="n">
-        <v>6941982</v>
+        <v>6941918</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1652,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1670,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133202465</v>
+        <v>133202427</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,42 +1713,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623786</v>
+        <v>623760</v>
       </c>
       <c r="R11" t="n">
-        <v>6941918</v>
+        <v>6941982</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1767,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,12 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,32 +1809,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133202424</v>
+        <v>133202429</v>
       </c>
       <c r="B12" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623813</v>
+        <v>623803</v>
       </c>
       <c r="R12" t="n">
-        <v>6941951</v>
+        <v>6942012</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133202426</v>
+        <v>133202436</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623801</v>
+        <v>623821</v>
       </c>
       <c r="R13" t="n">
-        <v>6941940</v>
+        <v>6942067</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,12 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>25 ex</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2023,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133202443</v>
+        <v>133202424</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623768</v>
+        <v>623813</v>
       </c>
       <c r="R14" t="n">
-        <v>6942054</v>
+        <v>6941951</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2098,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,12 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,32 +2130,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133202436</v>
+        <v>133202426</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623821</v>
+        <v>623801</v>
       </c>
       <c r="R15" t="n">
-        <v>6942067</v>
+        <v>6941940</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2210,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2210,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,32 +2242,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133202429</v>
+        <v>133202443</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623803</v>
+        <v>623768</v>
       </c>
       <c r="R16" t="n">
-        <v>6942012</v>
+        <v>6942054</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2327,7 +2322,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2685,7 +2685,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133202464</v>
+        <v>133202458</v>
       </c>
       <c r="B20" t="n">
         <v>57958</v>
@@ -2718,7 +2718,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623782</v>
+        <v>623770</v>
       </c>
       <c r="R20" t="n">
-        <v>6941914</v>
+        <v>6941875</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2773,12 +2773,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,7 +2805,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133202458</v>
+        <v>133202464</v>
       </c>
       <c r="B21" t="n">
         <v>57958</v>
@@ -2838,7 +2838,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623770</v>
+        <v>623782</v>
       </c>
       <c r="R21" t="n">
-        <v>6941875</v>
+        <v>6941914</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3246,10 +3246,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133202444</v>
+        <v>133202441</v>
       </c>
       <c r="B25" t="n">
-        <v>92338</v>
+        <v>57958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3257,34 +3257,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623743</v>
+        <v>623776</v>
       </c>
       <c r="R25" t="n">
-        <v>6942053</v>
+        <v>6942117</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3316,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3326,7 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,7 +3348,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3354,56 +3366,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133202441</v>
+        <v>133202455</v>
       </c>
       <c r="B26" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623776</v>
+        <v>623779</v>
       </c>
       <c r="R26" t="n">
-        <v>6942117</v>
+        <v>6941893</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3432,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3442,12 +3446,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>300+ ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,32 +3478,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133202455</v>
+        <v>133202444</v>
       </c>
       <c r="B27" t="n">
-        <v>99130</v>
+        <v>92338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6040186</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3509,13 +3513,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623779</v>
+        <v>623743</v>
       </c>
       <c r="R27" t="n">
-        <v>6941893</v>
+        <v>6942053</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3544,7 +3548,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3554,12 +3558,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>300+ ex</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3568,6 +3567,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4619,32 +4619,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133202431</v>
+        <v>133202430</v>
       </c>
       <c r="B37" t="n">
-        <v>80467</v>
+        <v>80438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4657,7 +4657,7 @@
         <v>623819</v>
       </c>
       <c r="R37" t="n">
-        <v>6942029</v>
+        <v>6942027</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,32 +4726,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133202430</v>
+        <v>133202431</v>
       </c>
       <c r="B38" t="n">
-        <v>80438</v>
+        <v>80467</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4764,7 +4764,7 @@
         <v>623819</v>
       </c>
       <c r="R38" t="n">
-        <v>6942027</v>
+        <v>6942029</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5276,32 +5276,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133240755</v>
+        <v>133240773</v>
       </c>
       <c r="B43" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623822</v>
+        <v>623688</v>
       </c>
       <c r="R43" t="n">
-        <v>6941942</v>
+        <v>6941982</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Spillning ( färskt)</t>
+          <t>27 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,32 +5388,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133240773</v>
+        <v>133240755</v>
       </c>
       <c r="B44" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623688</v>
+        <v>623822</v>
       </c>
       <c r="R44" t="n">
-        <v>6941982</v>
+        <v>6941942</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>27 ex</t>
+          <t>Spillning ( färskt)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5714,10 +5714,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133240763</v>
+        <v>133240766</v>
       </c>
       <c r="B47" t="n">
-        <v>92378</v>
+        <v>92566</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>483</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5749,13 +5749,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623739</v>
+        <v>623736</v>
       </c>
       <c r="R47" t="n">
-        <v>6942054</v>
+        <v>6942055</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5821,10 +5821,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133240766</v>
+        <v>133240763</v>
       </c>
       <c r="B48" t="n">
-        <v>92566</v>
+        <v>92378</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623736</v>
+        <v>623739</v>
       </c>
       <c r="R48" t="n">
-        <v>6942055</v>
+        <v>6942054</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5928,10 +5928,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133240760</v>
+        <v>133240772</v>
       </c>
       <c r="B49" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5939,21 +5939,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623830</v>
+        <v>623681</v>
       </c>
       <c r="R49" t="n">
-        <v>6942141</v>
+        <v>6942020</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6035,10 +6035,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133240772</v>
+        <v>133240760</v>
       </c>
       <c r="B50" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6046,21 +6046,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623681</v>
+        <v>623830</v>
       </c>
       <c r="R50" t="n">
-        <v>6942020</v>
+        <v>6942141</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6366,7 +6366,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133240758</v>
+        <v>133240767</v>
       </c>
       <c r="B53" t="n">
         <v>99130</v>
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>623824</v>
+        <v>623753</v>
       </c>
       <c r="R53" t="n">
-        <v>6941997</v>
+        <v>6942055</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>57 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6478,7 +6478,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133240767</v>
+        <v>133240764</v>
       </c>
       <c r="B54" t="n">
         <v>99130</v>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>623753</v>
+        <v>623736</v>
       </c>
       <c r="R54" t="n">
-        <v>6942055</v>
+        <v>6942051</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>57 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6590,7 +6590,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133240764</v>
+        <v>133240758</v>
       </c>
       <c r="B55" t="n">
         <v>99130</v>
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>623736</v>
+        <v>623824</v>
       </c>
       <c r="R55" t="n">
-        <v>6942051</v>
+        <v>6941997</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6702,7 +6702,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133240776</v>
+        <v>133240761</v>
       </c>
       <c r="B56" t="n">
         <v>99130</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>623720</v>
+        <v>623740</v>
       </c>
       <c r="R56" t="n">
-        <v>6941939</v>
+        <v>6942057</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>18 sex</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6814,7 +6814,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133240761</v>
+        <v>133240776</v>
       </c>
       <c r="B57" t="n">
         <v>99130</v>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>623740</v>
+        <v>623720</v>
       </c>
       <c r="R57" t="n">
-        <v>6942057</v>
+        <v>6941939</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>18 sex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -1582,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133202465</v>
+        <v>133202427</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,42 +1593,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623786</v>
+        <v>623760</v>
       </c>
       <c r="R10" t="n">
-        <v>6941918</v>
+        <v>6941982</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1660,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,12 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133202427</v>
+        <v>133202465</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,34 +1700,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623760</v>
+        <v>623786</v>
       </c>
       <c r="R11" t="n">
-        <v>6941982</v>
+        <v>6941918</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1772,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1777,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,32 +1809,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133202429</v>
+        <v>133202424</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623803</v>
+        <v>623813</v>
       </c>
       <c r="R12" t="n">
-        <v>6942012</v>
+        <v>6941951</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133202436</v>
+        <v>133202426</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623821</v>
+        <v>623801</v>
       </c>
       <c r="R13" t="n">
-        <v>6942067</v>
+        <v>6941940</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133202424</v>
+        <v>133202443</v>
       </c>
       <c r="B14" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2058,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623813</v>
+        <v>623768</v>
       </c>
       <c r="R14" t="n">
-        <v>6941951</v>
+        <v>6942054</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2093,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2108,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,32 +2140,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133202426</v>
+        <v>133202429</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623801</v>
+        <v>623803</v>
       </c>
       <c r="R15" t="n">
-        <v>6941940</v>
+        <v>6942012</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2200,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,12 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>25 ex</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,32 +2247,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133202443</v>
+        <v>133202436</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2282,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623768</v>
+        <v>623821</v>
       </c>
       <c r="R16" t="n">
-        <v>6942054</v>
+        <v>6942067</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2312,7 +2317,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,12 +2327,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2685,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133202458</v>
+        <v>133202454</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,42 +2696,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623770</v>
+        <v>623773</v>
       </c>
       <c r="R20" t="n">
-        <v>6941875</v>
+        <v>6941893</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2763,7 +2755,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2773,12 +2765,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,53 +2792,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133202464</v>
+        <v>133202460</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>92290</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623782</v>
+        <v>623768</v>
       </c>
       <c r="R21" t="n">
-        <v>6941914</v>
+        <v>6941880</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2883,7 +2862,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,12 +2872,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133202454</v>
+        <v>133202432</v>
       </c>
       <c r="B22" t="n">
-        <v>92217</v>
+        <v>91918</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,21 +2910,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2934,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623773</v>
+        <v>623820</v>
       </c>
       <c r="R22" t="n">
-        <v>6941893</v>
+        <v>6942033</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2995,7 +2969,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +2979,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,45 +3006,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133202460</v>
+        <v>133202458</v>
       </c>
       <c r="B23" t="n">
-        <v>92290</v>
+        <v>57958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623768</v>
+        <v>623770</v>
       </c>
       <c r="R23" t="n">
-        <v>6941880</v>
+        <v>6941875</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3102,7 +3084,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3094,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3126,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133202432</v>
+        <v>133202464</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3150,34 +3137,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623820</v>
+        <v>623782</v>
       </c>
       <c r="R24" t="n">
-        <v>6942033</v>
+        <v>6941914</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3209,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3219,7 +3214,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -1006,53 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202450</v>
+        <v>133202459</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623712</v>
+        <v>623775</v>
       </c>
       <c r="R5" t="n">
-        <v>6941985</v>
+        <v>6941872</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,12 +1086,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,53 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202461</v>
+        <v>133202438</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623727</v>
+        <v>623820</v>
       </c>
       <c r="R6" t="n">
-        <v>6941870</v>
+        <v>6942117</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,12 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,45 +1230,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202459</v>
+        <v>133202461</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623775</v>
+        <v>623727</v>
       </c>
       <c r="R7" t="n">
-        <v>6941872</v>
+        <v>6941870</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1318,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,45 +1350,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202438</v>
+        <v>133202450</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623820</v>
+        <v>623712</v>
       </c>
       <c r="R8" t="n">
-        <v>6942117</v>
+        <v>6941985</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2685,32 +2685,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133202454</v>
+        <v>133202460</v>
       </c>
       <c r="B20" t="n">
-        <v>92217</v>
+        <v>92290</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623773</v>
+        <v>623768</v>
       </c>
       <c r="R20" t="n">
-        <v>6941893</v>
+        <v>6941880</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,32 +2792,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133202460</v>
+        <v>133202432</v>
       </c>
       <c r="B21" t="n">
-        <v>92290</v>
+        <v>91918</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623768</v>
+        <v>623820</v>
       </c>
       <c r="R21" t="n">
-        <v>6941880</v>
+        <v>6942033</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133202432</v>
+        <v>133202454</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>92217</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,21 +2910,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623820</v>
+        <v>623773</v>
       </c>
       <c r="R22" t="n">
-        <v>6942033</v>
+        <v>6941893</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,7 +3006,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133202458</v>
+        <v>133202464</v>
       </c>
       <c r="B23" t="n">
         <v>57958</v>
@@ -3039,7 +3039,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623770</v>
+        <v>623782</v>
       </c>
       <c r="R23" t="n">
-        <v>6941875</v>
+        <v>6941914</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3126,7 +3126,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133202464</v>
+        <v>133202458</v>
       </c>
       <c r="B24" t="n">
         <v>57958</v>
@@ -3159,7 +3159,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623782</v>
+        <v>623770</v>
       </c>
       <c r="R24" t="n">
-        <v>6941914</v>
+        <v>6941875</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,56 +3246,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133202441</v>
+        <v>133202455</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623776</v>
+        <v>623779</v>
       </c>
       <c r="R25" t="n">
-        <v>6942117</v>
+        <v>6941893</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3316,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3326,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>300+ ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,32 +3358,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133202455</v>
+        <v>133202444</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>92338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6040186</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3401,13 +3393,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623779</v>
+        <v>623743</v>
       </c>
       <c r="R26" t="n">
-        <v>6941893</v>
+        <v>6942053</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3428,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,12 +3438,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>300+ ex</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,6 +3447,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3478,10 +3466,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133202444</v>
+        <v>133202441</v>
       </c>
       <c r="B27" t="n">
-        <v>92338</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,34 +3477,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623743</v>
+        <v>623776</v>
       </c>
       <c r="R27" t="n">
-        <v>6942053</v>
+        <v>6942117</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3548,7 +3544,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3558,7 +3554,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3567,7 +3568,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133202448</v>
+        <v>133202463</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3709,42 +3709,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623750</v>
+        <v>623712</v>
       </c>
       <c r="R29" t="n">
-        <v>6941932</v>
+        <v>6941856</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3776,7 +3768,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3786,12 +3778,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,10 +3805,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133202463</v>
+        <v>133202448</v>
       </c>
       <c r="B30" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,34 +3816,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623712</v>
+        <v>623750</v>
       </c>
       <c r="R30" t="n">
-        <v>6941856</v>
+        <v>6941932</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3888,7 +3883,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3898,7 +3893,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4272,7 +4272,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133202445</v>
+        <v>133202435</v>
       </c>
       <c r="B34" t="n">
         <v>57958</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623745</v>
+        <v>623795</v>
       </c>
       <c r="R34" t="n">
-        <v>6942050</v>
+        <v>6942074</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4392,7 +4392,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133202435</v>
+        <v>133202445</v>
       </c>
       <c r="B35" t="n">
         <v>57958</v>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623795</v>
+        <v>623745</v>
       </c>
       <c r="R35" t="n">
-        <v>6942074</v>
+        <v>6942050</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4619,32 +4619,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133202430</v>
+        <v>133202434</v>
       </c>
       <c r="B37" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623819</v>
+        <v>623790</v>
       </c>
       <c r="R37" t="n">
-        <v>6942027</v>
+        <v>6942049</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,7 +4699,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,32 +4731,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133202431</v>
+        <v>133202430</v>
       </c>
       <c r="B38" t="n">
-        <v>80467</v>
+        <v>80438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4764,7 +4769,7 @@
         <v>623819</v>
       </c>
       <c r="R38" t="n">
-        <v>6942029</v>
+        <v>6942027</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4796,7 +4801,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4806,7 +4811,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4833,32 +4838,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133202434</v>
+        <v>133202431</v>
       </c>
       <c r="B39" t="n">
-        <v>99130</v>
+        <v>80467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4868,10 +4873,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623790</v>
+        <v>623819</v>
       </c>
       <c r="R39" t="n">
-        <v>6942049</v>
+        <v>6942029</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4903,7 +4908,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4913,12 +4918,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5276,32 +5276,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133240773</v>
+        <v>133240755</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623688</v>
+        <v>623822</v>
       </c>
       <c r="R43" t="n">
-        <v>6941982</v>
+        <v>6941942</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>27 ex</t>
+          <t>Spillning ( färskt)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,32 +5388,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133240755</v>
+        <v>133240773</v>
       </c>
       <c r="B44" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623822</v>
+        <v>623688</v>
       </c>
       <c r="R44" t="n">
-        <v>6941942</v>
+        <v>6941982</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Spillning ( färskt)</t>
+          <t>27 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5714,10 +5714,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133240766</v>
+        <v>133240763</v>
       </c>
       <c r="B47" t="n">
-        <v>92566</v>
+        <v>92378</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>483</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5749,13 +5749,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623736</v>
+        <v>623739</v>
       </c>
       <c r="R47" t="n">
-        <v>6942055</v>
+        <v>6942054</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5821,10 +5821,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133240763</v>
+        <v>133240766</v>
       </c>
       <c r="B48" t="n">
-        <v>92378</v>
+        <v>92566</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>483</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623739</v>
+        <v>623736</v>
       </c>
       <c r="R48" t="n">
-        <v>6942054</v>
+        <v>6942055</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -899,48 +899,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133202423</v>
+        <v>133202461</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623825</v>
+        <v>623727</v>
       </c>
       <c r="R4" t="n">
-        <v>6941925</v>
+        <v>6941870</v>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +987,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +1019,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202459</v>
+        <v>133202450</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623775</v>
+        <v>623712</v>
       </c>
       <c r="R5" t="n">
-        <v>6941872</v>
+        <v>6941985</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1107,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202438</v>
+        <v>133202459</v>
       </c>
       <c r="B6" t="n">
         <v>99130</v>
@@ -1153,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623820</v>
+        <v>623775</v>
       </c>
       <c r="R6" t="n">
-        <v>6942117</v>
+        <v>6941872</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1188,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1219,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,53 +1251,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202461</v>
+        <v>133202438</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623727</v>
+        <v>623820</v>
       </c>
       <c r="R7" t="n">
-        <v>6941870</v>
+        <v>6942117</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,12 +1331,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,56 +1363,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202450</v>
+        <v>133202423</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623712</v>
+        <v>623825</v>
       </c>
       <c r="R8" t="n">
-        <v>6941985</v>
+        <v>6941925</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1809,32 +1809,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133202424</v>
+        <v>133202429</v>
       </c>
       <c r="B12" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623813</v>
+        <v>623803</v>
       </c>
       <c r="R12" t="n">
-        <v>6941951</v>
+        <v>6942012</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133202426</v>
+        <v>133202436</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623801</v>
+        <v>623821</v>
       </c>
       <c r="R13" t="n">
-        <v>6941940</v>
+        <v>6942067</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,12 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>25 ex</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2023,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133202443</v>
+        <v>133202424</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623768</v>
+        <v>623813</v>
       </c>
       <c r="R14" t="n">
-        <v>6942054</v>
+        <v>6941951</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2098,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,12 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,32 +2130,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133202429</v>
+        <v>133202426</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623803</v>
+        <v>623801</v>
       </c>
       <c r="R15" t="n">
-        <v>6942012</v>
+        <v>6941940</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2210,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2210,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,32 +2242,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133202436</v>
+        <v>133202443</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623821</v>
+        <v>623768</v>
       </c>
       <c r="R16" t="n">
-        <v>6942067</v>
+        <v>6942054</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2327,7 +2322,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,32 +2354,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133202453</v>
+        <v>133202452</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2389,13 +2389,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623773</v>
+        <v>623775</v>
       </c>
       <c r="R17" t="n">
-        <v>6941896</v>
+        <v>6941903</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2434,12 +2434,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,7 +2461,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133202442</v>
+        <v>133202453</v>
       </c>
       <c r="B18" t="n">
         <v>99130</v>
@@ -2501,13 +2496,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623770</v>
+        <v>623773</v>
       </c>
       <c r="R18" t="n">
-        <v>6942069</v>
+        <v>6941896</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2536,7 +2531,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2546,12 +2541,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2578,32 +2573,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133202452</v>
+        <v>133202442</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2613,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623775</v>
+        <v>623770</v>
       </c>
       <c r="R19" t="n">
-        <v>6941903</v>
+        <v>6942069</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2648,7 +2643,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2658,7 +2653,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -5928,32 +5928,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133240772</v>
+        <v>133240771</v>
       </c>
       <c r="B49" t="n">
-        <v>91932</v>
+        <v>99130</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623681</v>
+        <v>623737</v>
       </c>
       <c r="R49" t="n">
-        <v>6942020</v>
+        <v>6942012</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6008,7 +6008,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6035,10 +6040,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133240760</v>
+        <v>133240772</v>
       </c>
       <c r="B50" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6046,21 +6051,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623830</v>
+        <v>623681</v>
       </c>
       <c r="R50" t="n">
-        <v>6942141</v>
+        <v>6942020</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6105,7 +6110,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6115,7 +6120,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6142,32 +6147,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133240771</v>
+        <v>133240760</v>
       </c>
       <c r="B51" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6177,10 +6182,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623737</v>
+        <v>623830</v>
       </c>
       <c r="R51" t="n">
-        <v>6942012</v>
+        <v>6942141</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6212,7 +6217,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6222,12 +6227,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -899,56 +899,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133202461</v>
+        <v>133202423</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623727</v>
+        <v>623825</v>
       </c>
       <c r="R4" t="n">
-        <v>6941870</v>
+        <v>6941925</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,53 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202450</v>
+        <v>133202459</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623712</v>
+        <v>623775</v>
       </c>
       <c r="R5" t="n">
-        <v>6941985</v>
+        <v>6941872</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,12 +1086,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202459</v>
+        <v>133202438</v>
       </c>
       <c r="B6" t="n">
         <v>99130</v>
@@ -1174,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623775</v>
+        <v>623820</v>
       </c>
       <c r="R6" t="n">
-        <v>6941872</v>
+        <v>6942117</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,12 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,45 +1230,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202438</v>
+        <v>133202461</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623820</v>
+        <v>623727</v>
       </c>
       <c r="R7" t="n">
-        <v>6942117</v>
+        <v>6941870</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,12 +1318,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,48 +1350,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202423</v>
+        <v>133202450</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623825</v>
+        <v>623712</v>
       </c>
       <c r="R8" t="n">
-        <v>6941925</v>
+        <v>6941985</v>
       </c>
       <c r="S8" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1438,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2354,32 +2354,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133202452</v>
+        <v>133202453</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2389,13 +2389,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623775</v>
+        <v>623773</v>
       </c>
       <c r="R17" t="n">
-        <v>6941903</v>
+        <v>6941896</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2434,7 +2434,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2461,7 +2466,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133202453</v>
+        <v>133202442</v>
       </c>
       <c r="B18" t="n">
         <v>99130</v>
@@ -2496,13 +2501,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623773</v>
+        <v>623770</v>
       </c>
       <c r="R18" t="n">
-        <v>6941896</v>
+        <v>6942069</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2531,7 +2536,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2541,12 +2546,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,32 +2578,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133202442</v>
+        <v>133202452</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623770</v>
+        <v>623775</v>
       </c>
       <c r="R19" t="n">
-        <v>6942069</v>
+        <v>6941903</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2643,7 +2648,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,12 +2658,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -5714,10 +5714,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133240763</v>
+        <v>133240766</v>
       </c>
       <c r="B47" t="n">
-        <v>92378</v>
+        <v>92566</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>483</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5749,13 +5749,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623739</v>
+        <v>623736</v>
       </c>
       <c r="R47" t="n">
-        <v>6942054</v>
+        <v>6942055</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5821,10 +5821,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133240766</v>
+        <v>133240763</v>
       </c>
       <c r="B48" t="n">
-        <v>92566</v>
+        <v>92378</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623736</v>
+        <v>623739</v>
       </c>
       <c r="R48" t="n">
-        <v>6942055</v>
+        <v>6942054</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -1809,32 +1809,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133202429</v>
+        <v>133202424</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623803</v>
+        <v>623813</v>
       </c>
       <c r="R12" t="n">
-        <v>6942012</v>
+        <v>6941951</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133202436</v>
+        <v>133202426</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623821</v>
+        <v>623801</v>
       </c>
       <c r="R13" t="n">
-        <v>6942067</v>
+        <v>6941940</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133202424</v>
+        <v>133202443</v>
       </c>
       <c r="B14" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2058,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623813</v>
+        <v>623768</v>
       </c>
       <c r="R14" t="n">
-        <v>6941951</v>
+        <v>6942054</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2093,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2108,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,32 +2140,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133202426</v>
+        <v>133202429</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623801</v>
+        <v>623803</v>
       </c>
       <c r="R15" t="n">
-        <v>6941940</v>
+        <v>6942012</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2200,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,12 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>25 ex</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,32 +2247,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133202443</v>
+        <v>133202436</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2282,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623768</v>
+        <v>623821</v>
       </c>
       <c r="R16" t="n">
-        <v>6942054</v>
+        <v>6942067</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2312,7 +2317,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,12 +2327,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,32 +2354,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133202453</v>
+        <v>133202452</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2389,13 +2389,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623773</v>
+        <v>623775</v>
       </c>
       <c r="R17" t="n">
-        <v>6941896</v>
+        <v>6941903</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2434,12 +2434,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,7 +2461,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133202442</v>
+        <v>133202453</v>
       </c>
       <c r="B18" t="n">
         <v>99130</v>
@@ -2501,13 +2496,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623770</v>
+        <v>623773</v>
       </c>
       <c r="R18" t="n">
-        <v>6942069</v>
+        <v>6941896</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2536,7 +2531,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2546,12 +2541,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2578,32 +2573,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133202452</v>
+        <v>133202442</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2613,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623775</v>
+        <v>623770</v>
       </c>
       <c r="R19" t="n">
-        <v>6941903</v>
+        <v>6942069</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2648,7 +2643,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2658,7 +2653,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4045,10 +4045,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133202440</v>
+        <v>133202437</v>
       </c>
       <c r="B32" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,34 +4056,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623827</v>
+        <v>623840</v>
       </c>
       <c r="R32" t="n">
-        <v>6942150</v>
+        <v>6942067</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4115,7 +4123,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4125,7 +4133,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,10 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133202437</v>
+        <v>133202440</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,42 +4176,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623840</v>
+        <v>623827</v>
       </c>
       <c r="R33" t="n">
-        <v>6942067</v>
+        <v>6942150</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4230,7 +4235,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4240,12 +4245,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -899,48 +899,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133202423</v>
+        <v>133202461</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623825</v>
+        <v>623727</v>
       </c>
       <c r="R4" t="n">
-        <v>6941925</v>
+        <v>6941870</v>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +987,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +1019,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202459</v>
+        <v>133202450</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623775</v>
+        <v>623712</v>
       </c>
       <c r="R5" t="n">
-        <v>6941872</v>
+        <v>6941985</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1107,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202438</v>
+        <v>133202459</v>
       </c>
       <c r="B6" t="n">
         <v>99130</v>
@@ -1153,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623820</v>
+        <v>623775</v>
       </c>
       <c r="R6" t="n">
-        <v>6942117</v>
+        <v>6941872</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1188,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1219,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,53 +1251,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202461</v>
+        <v>133202438</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623727</v>
+        <v>623820</v>
       </c>
       <c r="R7" t="n">
-        <v>6941870</v>
+        <v>6942117</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,12 +1331,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,56 +1363,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202450</v>
+        <v>133202423</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623712</v>
+        <v>623825</v>
       </c>
       <c r="R8" t="n">
-        <v>6941985</v>
+        <v>6941925</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2354,32 +2354,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133202452</v>
+        <v>133202453</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2389,13 +2389,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623775</v>
+        <v>623773</v>
       </c>
       <c r="R17" t="n">
-        <v>6941903</v>
+        <v>6941896</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2434,7 +2434,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2461,7 +2466,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133202453</v>
+        <v>133202442</v>
       </c>
       <c r="B18" t="n">
         <v>99130</v>
@@ -2496,13 +2501,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623773</v>
+        <v>623770</v>
       </c>
       <c r="R18" t="n">
-        <v>6941896</v>
+        <v>6942069</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2531,7 +2536,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2541,12 +2546,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,32 +2578,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133202442</v>
+        <v>133202452</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623770</v>
+        <v>623775</v>
       </c>
       <c r="R19" t="n">
-        <v>6942069</v>
+        <v>6941903</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2643,7 +2648,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,12 +2658,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133202433</v>
       </c>
       <c r="B2" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133202425</v>
       </c>
       <c r="B3" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,53 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133202461</v>
+        <v>133202459</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>99132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623727</v>
+        <v>623775</v>
       </c>
       <c r="R4" t="n">
-        <v>6941870</v>
+        <v>6941872</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,53 +1011,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202450</v>
+        <v>133202438</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>99132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623712</v>
+        <v>623820</v>
       </c>
       <c r="R5" t="n">
-        <v>6941985</v>
+        <v>6942117</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202459</v>
+        <v>133202423</v>
       </c>
       <c r="B6" t="n">
-        <v>99130</v>
+        <v>91883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623775</v>
+        <v>623825</v>
       </c>
       <c r="R6" t="n">
-        <v>6941872</v>
+        <v>6941925</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,12 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,45 +1230,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202438</v>
+        <v>133202450</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623820</v>
+        <v>623712</v>
       </c>
       <c r="R7" t="n">
-        <v>6942117</v>
+        <v>6941985</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,12 +1318,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,48 +1350,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202423</v>
+        <v>133202461</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623825</v>
+        <v>623727</v>
       </c>
       <c r="R8" t="n">
-        <v>6941925</v>
+        <v>6941870</v>
       </c>
       <c r="S8" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1438,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,7 +1473,7 @@
         <v>133202446</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133202427</v>
+        <v>133202465</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,34 +1593,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623760</v>
+        <v>623786</v>
       </c>
       <c r="R10" t="n">
-        <v>6941982</v>
+        <v>6941918</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1652,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1670,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133202465</v>
+        <v>133202427</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,42 +1713,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623786</v>
+        <v>623760</v>
       </c>
       <c r="R11" t="n">
-        <v>6941918</v>
+        <v>6941982</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1767,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,12 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,32 +1809,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133202424</v>
+        <v>133202426</v>
       </c>
       <c r="B12" t="n">
-        <v>97995</v>
+        <v>99132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623813</v>
+        <v>623801</v>
       </c>
       <c r="R12" t="n">
-        <v>6941951</v>
+        <v>6941940</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133202426</v>
+        <v>133202443</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623801</v>
+        <v>623768</v>
       </c>
       <c r="R13" t="n">
-        <v>6941940</v>
+        <v>6942054</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1986,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,12 +2001,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2033,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133202443</v>
+        <v>133202424</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>97997</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623768</v>
+        <v>623813</v>
       </c>
       <c r="R14" t="n">
-        <v>6942054</v>
+        <v>6941951</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2098,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,12 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,7 +2143,7 @@
         <v>133202429</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>133202436</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>133202453</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>133202442</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>133202452</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2685,32 +2685,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133202460</v>
+        <v>133202454</v>
       </c>
       <c r="B20" t="n">
-        <v>92290</v>
+        <v>92219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623768</v>
+        <v>623773</v>
       </c>
       <c r="R20" t="n">
-        <v>6941880</v>
+        <v>6941893</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2795,7 +2795,7 @@
         <v>133202432</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133202454</v>
+        <v>133202458</v>
       </c>
       <c r="B22" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,34 +2910,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623773</v>
+        <v>623770</v>
       </c>
       <c r="R22" t="n">
-        <v>6941893</v>
+        <v>6941875</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2969,7 +2977,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2987,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3126,53 +3139,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133202458</v>
+        <v>133202460</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>92292</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623770</v>
+        <v>623768</v>
       </c>
       <c r="R24" t="n">
-        <v>6941875</v>
+        <v>6941880</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3204,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3214,12 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,7 +3249,7 @@
         <v>133202455</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>133202444</v>
       </c>
       <c r="B26" t="n">
-        <v>92338</v>
+        <v>92340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>133202451</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>133202463</v>
       </c>
       <c r="B29" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133202437</v>
+        <v>133202440</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,42 +4056,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623840</v>
+        <v>623827</v>
       </c>
       <c r="R32" t="n">
-        <v>6942067</v>
+        <v>6942150</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4123,7 +4115,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4133,12 +4125,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,10 +4152,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133202440</v>
+        <v>133202437</v>
       </c>
       <c r="B33" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4176,34 +4163,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623827</v>
+        <v>623840</v>
       </c>
       <c r="R33" t="n">
-        <v>6942150</v>
+        <v>6942067</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4235,7 +4230,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4245,7 +4240,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4272,7 +4272,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133202435</v>
+        <v>133202445</v>
       </c>
       <c r="B34" t="n">
         <v>57958</v>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623795</v>
+        <v>623745</v>
       </c>
       <c r="R34" t="n">
-        <v>6942074</v>
+        <v>6942050</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4392,7 +4392,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133202445</v>
+        <v>133202435</v>
       </c>
       <c r="B35" t="n">
         <v>57958</v>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623745</v>
+        <v>623795</v>
       </c>
       <c r="R35" t="n">
-        <v>6942050</v>
+        <v>6942074</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,7 +4515,7 @@
         <v>133202456</v>
       </c>
       <c r="B36" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4619,32 +4619,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133202434</v>
+        <v>133202430</v>
       </c>
       <c r="B37" t="n">
-        <v>99130</v>
+        <v>80439</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623790</v>
+        <v>623819</v>
       </c>
       <c r="R37" t="n">
-        <v>6942049</v>
+        <v>6942027</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,12 +4699,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4731,32 +4726,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133202430</v>
+        <v>133202431</v>
       </c>
       <c r="B38" t="n">
-        <v>80438</v>
+        <v>80468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4769,7 +4764,7 @@
         <v>623819</v>
       </c>
       <c r="R38" t="n">
-        <v>6942027</v>
+        <v>6942029</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4801,7 +4796,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4811,7 +4806,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,32 +4833,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133202431</v>
+        <v>133202434</v>
       </c>
       <c r="B39" t="n">
-        <v>80467</v>
+        <v>99132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4873,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623819</v>
+        <v>623790</v>
       </c>
       <c r="R39" t="n">
-        <v>6942029</v>
+        <v>6942049</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4908,7 +4903,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4918,7 +4913,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4948,7 +4948,7 @@
         <v>133202439</v>
       </c>
       <c r="B40" t="n">
-        <v>92214</v>
+        <v>92216</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>133240775</v>
       </c>
       <c r="B41" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>133240757</v>
       </c>
       <c r="B42" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133240755</v>
+        <v>133240773</v>
       </c>
       <c r="B43" t="n">
-        <v>56522</v>
+        <v>99132</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623822</v>
+        <v>623688</v>
       </c>
       <c r="R43" t="n">
-        <v>6941942</v>
+        <v>6941982</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Spillning ( färskt)</t>
+          <t>27 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,32 +5388,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133240773</v>
+        <v>133240755</v>
       </c>
       <c r="B44" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623688</v>
+        <v>623822</v>
       </c>
       <c r="R44" t="n">
-        <v>6941982</v>
+        <v>6941942</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>27 ex</t>
+          <t>Spillning ( färskt)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5503,7 +5503,7 @@
         <v>133240774</v>
       </c>
       <c r="B45" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>133240762</v>
       </c>
       <c r="B46" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>133240766</v>
       </c>
       <c r="B47" t="n">
-        <v>92566</v>
+        <v>92568</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>133240763</v>
       </c>
       <c r="B48" t="n">
-        <v>92378</v>
+        <v>92380</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5928,32 +5928,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133240771</v>
+        <v>133240772</v>
       </c>
       <c r="B49" t="n">
-        <v>99130</v>
+        <v>91934</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623737</v>
+        <v>623681</v>
       </c>
       <c r="R49" t="n">
-        <v>6942012</v>
+        <v>6942020</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6008,12 +6008,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6040,10 +6035,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133240772</v>
+        <v>133240760</v>
       </c>
       <c r="B50" t="n">
-        <v>91932</v>
+        <v>91920</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6051,21 +6046,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623681</v>
+        <v>623830</v>
       </c>
       <c r="R50" t="n">
-        <v>6942020</v>
+        <v>6942141</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6110,7 +6105,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6120,7 +6115,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6147,32 +6142,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133240760</v>
+        <v>133240771</v>
       </c>
       <c r="B51" t="n">
-        <v>91918</v>
+        <v>99132</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6182,10 +6177,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623830</v>
+        <v>623737</v>
       </c>
       <c r="R51" t="n">
-        <v>6942141</v>
+        <v>6942012</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6217,7 +6212,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6227,7 +6222,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6369,7 +6369,7 @@
         <v>133240767</v>
       </c>
       <c r="B53" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>133240764</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>133240758</v>
       </c>
       <c r="B55" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>133240761</v>
       </c>
       <c r="B56" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>133240776</v>
       </c>
       <c r="B57" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>133240754</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>133240759</v>
       </c>
       <c r="B59" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>133240777</v>
       </c>
       <c r="B60" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>133240756</v>
       </c>
       <c r="B61" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -2685,32 +2685,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133202454</v>
+        <v>133202460</v>
       </c>
       <c r="B20" t="n">
-        <v>92219</v>
+        <v>92292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623773</v>
+        <v>623768</v>
       </c>
       <c r="R20" t="n">
-        <v>6941893</v>
+        <v>6941880</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,10 +2792,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133202432</v>
+        <v>133202454</v>
       </c>
       <c r="B21" t="n">
-        <v>91920</v>
+        <v>92219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623820</v>
+        <v>623773</v>
       </c>
       <c r="R21" t="n">
-        <v>6942033</v>
+        <v>6941893</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133202458</v>
+        <v>133202432</v>
       </c>
       <c r="B22" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,42 +2910,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623770</v>
+        <v>623820</v>
       </c>
       <c r="R22" t="n">
-        <v>6941875</v>
+        <v>6942033</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2977,7 +2969,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2987,12 +2979,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3019,7 +3006,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133202464</v>
+        <v>133202458</v>
       </c>
       <c r="B23" t="n">
         <v>57958</v>
@@ -3052,7 +3039,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3062,10 +3049,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623782</v>
+        <v>623770</v>
       </c>
       <c r="R23" t="n">
-        <v>6941914</v>
+        <v>6941875</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3097,7 +3084,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3107,12 +3094,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,45 +3126,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133202460</v>
+        <v>133202464</v>
       </c>
       <c r="B24" t="n">
-        <v>92292</v>
+        <v>57958</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623768</v>
+        <v>623782</v>
       </c>
       <c r="R24" t="n">
-        <v>6941880</v>
+        <v>6941914</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3209,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3219,7 +3214,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4619,32 +4619,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133202430</v>
+        <v>133202434</v>
       </c>
       <c r="B37" t="n">
-        <v>80439</v>
+        <v>99132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623819</v>
+        <v>623790</v>
       </c>
       <c r="R37" t="n">
-        <v>6942027</v>
+        <v>6942049</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,7 +4699,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,32 +4731,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133202431</v>
+        <v>133202430</v>
       </c>
       <c r="B38" t="n">
-        <v>80468</v>
+        <v>80439</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4764,7 +4769,7 @@
         <v>623819</v>
       </c>
       <c r="R38" t="n">
-        <v>6942029</v>
+        <v>6942027</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4796,7 +4801,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4806,7 +4811,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4833,32 +4838,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133202434</v>
+        <v>133202431</v>
       </c>
       <c r="B39" t="n">
-        <v>99132</v>
+        <v>80468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4868,10 +4873,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623790</v>
+        <v>623819</v>
       </c>
       <c r="R39" t="n">
-        <v>6942049</v>
+        <v>6942029</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4903,7 +4908,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4913,12 +4918,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5928,32 +5928,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133240772</v>
+        <v>133240771</v>
       </c>
       <c r="B49" t="n">
-        <v>91934</v>
+        <v>99132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623681</v>
+        <v>623737</v>
       </c>
       <c r="R49" t="n">
-        <v>6942020</v>
+        <v>6942012</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6008,7 +6008,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6035,10 +6040,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133240760</v>
+        <v>133240772</v>
       </c>
       <c r="B50" t="n">
-        <v>91920</v>
+        <v>91934</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6046,21 +6051,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623830</v>
+        <v>623681</v>
       </c>
       <c r="R50" t="n">
-        <v>6942141</v>
+        <v>6942020</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6105,7 +6110,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6115,7 +6120,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6142,32 +6147,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133240771</v>
+        <v>133240760</v>
       </c>
       <c r="B51" t="n">
-        <v>99132</v>
+        <v>91920</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6177,10 +6182,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623737</v>
+        <v>623830</v>
       </c>
       <c r="R51" t="n">
-        <v>6942012</v>
+        <v>6942141</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6212,7 +6217,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6222,12 +6227,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133202459</v>
+        <v>133202423</v>
       </c>
       <c r="B4" t="n">
-        <v>99132</v>
+        <v>91883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623775</v>
+        <v>623825</v>
       </c>
       <c r="R4" t="n">
-        <v>6941872</v>
+        <v>6941925</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,45 +1006,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202438</v>
+        <v>133202450</v>
       </c>
       <c r="B5" t="n">
-        <v>99132</v>
+        <v>57958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623820</v>
+        <v>623712</v>
       </c>
       <c r="R5" t="n">
-        <v>6942117</v>
+        <v>6941985</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1094,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,48 +1126,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202423</v>
+        <v>133202461</v>
       </c>
       <c r="B6" t="n">
-        <v>91883</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623825</v>
+        <v>623727</v>
       </c>
       <c r="R6" t="n">
-        <v>6941925</v>
+        <v>6941870</v>
       </c>
       <c r="S6" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1214,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,53 +1246,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202450</v>
+        <v>133202459</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>99132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623712</v>
+        <v>623775</v>
       </c>
       <c r="R7" t="n">
-        <v>6941985</v>
+        <v>6941872</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,53 +1358,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202461</v>
+        <v>133202438</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>99132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623727</v>
+        <v>623820</v>
       </c>
       <c r="R8" t="n">
-        <v>6941870</v>
+        <v>6942117</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1582,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133202465</v>
+        <v>133202427</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,42 +1593,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623786</v>
+        <v>623760</v>
       </c>
       <c r="R10" t="n">
-        <v>6941918</v>
+        <v>6941982</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1660,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,12 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133202427</v>
+        <v>133202465</v>
       </c>
       <c r="B11" t="n">
-        <v>91920</v>
+        <v>57958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,34 +1700,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623760</v>
+        <v>623786</v>
       </c>
       <c r="R11" t="n">
-        <v>6941982</v>
+        <v>6941918</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1772,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1777,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,32 +1809,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133202426</v>
+        <v>133202429</v>
       </c>
       <c r="B12" t="n">
-        <v>99132</v>
+        <v>91920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623801</v>
+        <v>623803</v>
       </c>
       <c r="R12" t="n">
-        <v>6941940</v>
+        <v>6942012</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,12 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>25 ex</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133202443</v>
+        <v>133202436</v>
       </c>
       <c r="B13" t="n">
-        <v>99132</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623768</v>
+        <v>623821</v>
       </c>
       <c r="R13" t="n">
-        <v>6942054</v>
+        <v>6942067</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1991,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,12 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,32 +2130,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133202429</v>
+        <v>133202426</v>
       </c>
       <c r="B15" t="n">
-        <v>91920</v>
+        <v>99132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623803</v>
+        <v>623801</v>
       </c>
       <c r="R15" t="n">
-        <v>6942012</v>
+        <v>6941940</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2210,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2210,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,32 +2242,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133202436</v>
+        <v>133202443</v>
       </c>
       <c r="B16" t="n">
-        <v>91920</v>
+        <v>99132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623821</v>
+        <v>623768</v>
       </c>
       <c r="R16" t="n">
-        <v>6942067</v>
+        <v>6942054</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2327,7 +2322,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,32 +2354,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133202453</v>
+        <v>133202452</v>
       </c>
       <c r="B17" t="n">
-        <v>99132</v>
+        <v>91920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2389,13 +2389,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623773</v>
+        <v>623775</v>
       </c>
       <c r="R17" t="n">
-        <v>6941896</v>
+        <v>6941903</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2434,12 +2434,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,7 +2461,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133202442</v>
+        <v>133202453</v>
       </c>
       <c r="B18" t="n">
         <v>99132</v>
@@ -2501,13 +2496,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623770</v>
+        <v>623773</v>
       </c>
       <c r="R18" t="n">
-        <v>6942069</v>
+        <v>6941896</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2536,7 +2531,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2546,12 +2541,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2578,32 +2573,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133202452</v>
+        <v>133202442</v>
       </c>
       <c r="B19" t="n">
-        <v>91920</v>
+        <v>99132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2613,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623775</v>
+        <v>623770</v>
       </c>
       <c r="R19" t="n">
-        <v>6941903</v>
+        <v>6942069</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2648,7 +2643,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2658,7 +2653,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4045,10 +4045,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133202440</v>
+        <v>133202437</v>
       </c>
       <c r="B32" t="n">
-        <v>91920</v>
+        <v>57958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,34 +4056,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623827</v>
+        <v>623840</v>
       </c>
       <c r="R32" t="n">
-        <v>6942150</v>
+        <v>6942067</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4115,7 +4123,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4125,7 +4133,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,10 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133202437</v>
+        <v>133202440</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,42 +4176,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623840</v>
+        <v>623827</v>
       </c>
       <c r="R33" t="n">
-        <v>6942067</v>
+        <v>6942150</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4230,7 +4235,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4240,12 +4245,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133202433</v>
+        <v>133202425</v>
       </c>
       <c r="B2" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623817</v>
+        <v>623809</v>
       </c>
       <c r="R2" t="n">
-        <v>6942024</v>
+        <v>6941943</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133202425</v>
+        <v>133202433</v>
       </c>
       <c r="B3" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623809</v>
+        <v>623817</v>
       </c>
       <c r="R3" t="n">
-        <v>6941943</v>
+        <v>6942024</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>133202423</v>
       </c>
       <c r="B4" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>133202459</v>
       </c>
       <c r="B7" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>133202438</v>
       </c>
       <c r="B8" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>133202446</v>
       </c>
       <c r="B9" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>133202427</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>133202429</v>
       </c>
       <c r="B12" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>133202436</v>
       </c>
       <c r="B13" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>133202424</v>
       </c>
       <c r="B14" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>133202426</v>
       </c>
       <c r="B15" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>133202443</v>
       </c>
       <c r="B16" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>133202452</v>
       </c>
       <c r="B17" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>133202453</v>
       </c>
       <c r="B18" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>133202442</v>
       </c>
       <c r="B19" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2685,32 +2685,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133202460</v>
+        <v>133202454</v>
       </c>
       <c r="B20" t="n">
-        <v>92292</v>
+        <v>92227</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623768</v>
+        <v>623773</v>
       </c>
       <c r="R20" t="n">
-        <v>6941880</v>
+        <v>6941893</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,10 +2792,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133202454</v>
+        <v>133202432</v>
       </c>
       <c r="B21" t="n">
-        <v>92219</v>
+        <v>91928</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623773</v>
+        <v>623820</v>
       </c>
       <c r="R21" t="n">
-        <v>6941893</v>
+        <v>6942033</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,32 +2899,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133202432</v>
+        <v>133202460</v>
       </c>
       <c r="B22" t="n">
-        <v>91920</v>
+        <v>92300</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623820</v>
+        <v>623768</v>
       </c>
       <c r="R22" t="n">
-        <v>6942033</v>
+        <v>6941880</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3246,48 +3246,56 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133202455</v>
+        <v>133202441</v>
       </c>
       <c r="B25" t="n">
-        <v>99132</v>
+        <v>57958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623779</v>
+        <v>623776</v>
       </c>
       <c r="R25" t="n">
-        <v>6941893</v>
+        <v>6942117</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3316,7 +3324,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3326,12 +3334,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>300+ ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3358,32 +3366,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133202444</v>
+        <v>133202455</v>
       </c>
       <c r="B26" t="n">
-        <v>92340</v>
+        <v>99140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3393,13 +3401,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623743</v>
+        <v>623779</v>
       </c>
       <c r="R26" t="n">
-        <v>6942053</v>
+        <v>6941893</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3428,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3438,7 +3446,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>300+ ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3447,7 +3460,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3466,10 +3478,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133202441</v>
+        <v>133202444</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>92348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3477,42 +3489,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623776</v>
+        <v>623743</v>
       </c>
       <c r="R27" t="n">
-        <v>6942117</v>
+        <v>6942053</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3544,7 +3548,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3554,12 +3558,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3568,6 +3567,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>133202451</v>
       </c>
       <c r="B28" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>133202463</v>
       </c>
       <c r="B29" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>133202440</v>
       </c>
       <c r="B33" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>133202456</v>
       </c>
       <c r="B36" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4619,32 +4619,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133202434</v>
+        <v>133202430</v>
       </c>
       <c r="B37" t="n">
-        <v>99132</v>
+        <v>80439</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623790</v>
+        <v>623819</v>
       </c>
       <c r="R37" t="n">
-        <v>6942049</v>
+        <v>6942027</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,12 +4699,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4731,32 +4726,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133202430</v>
+        <v>133202434</v>
       </c>
       <c r="B38" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4766,10 +4761,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>623819</v>
+        <v>623790</v>
       </c>
       <c r="R38" t="n">
-        <v>6942027</v>
+        <v>6942049</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4801,7 +4796,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4811,7 +4806,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4948,7 +4948,7 @@
         <v>133202439</v>
       </c>
       <c r="B40" t="n">
-        <v>92216</v>
+        <v>92224</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>133240775</v>
       </c>
       <c r="B41" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>133240757</v>
       </c>
       <c r="B42" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133240773</v>
+        <v>133240755</v>
       </c>
       <c r="B43" t="n">
-        <v>99132</v>
+        <v>56522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623688</v>
+        <v>623822</v>
       </c>
       <c r="R43" t="n">
-        <v>6941982</v>
+        <v>6941942</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>27 ex</t>
+          <t>Spillning ( färskt)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,32 +5388,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133240755</v>
+        <v>133240773</v>
       </c>
       <c r="B44" t="n">
-        <v>56522</v>
+        <v>99140</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623822</v>
+        <v>623688</v>
       </c>
       <c r="R44" t="n">
-        <v>6941942</v>
+        <v>6941982</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Spillning ( färskt)</t>
+          <t>27 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5610,7 +5610,7 @@
         <v>133240762</v>
       </c>
       <c r="B46" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>133240766</v>
       </c>
       <c r="B47" t="n">
-        <v>92568</v>
+        <v>92576</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>133240763</v>
       </c>
       <c r="B48" t="n">
-        <v>92380</v>
+        <v>92388</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5928,32 +5928,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133240771</v>
+        <v>133240772</v>
       </c>
       <c r="B49" t="n">
-        <v>99132</v>
+        <v>91942</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623737</v>
+        <v>623681</v>
       </c>
       <c r="R49" t="n">
-        <v>6942012</v>
+        <v>6942020</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6008,12 +6008,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6040,10 +6035,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133240772</v>
+        <v>133240760</v>
       </c>
       <c r="B50" t="n">
-        <v>91934</v>
+        <v>91928</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6051,21 +6046,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623681</v>
+        <v>623830</v>
       </c>
       <c r="R50" t="n">
-        <v>6942020</v>
+        <v>6942141</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6110,7 +6105,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6120,7 +6115,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6147,32 +6142,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133240760</v>
+        <v>133240771</v>
       </c>
       <c r="B51" t="n">
-        <v>91920</v>
+        <v>99140</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6182,10 +6177,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623830</v>
+        <v>623737</v>
       </c>
       <c r="R51" t="n">
-        <v>6942141</v>
+        <v>6942012</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6217,7 +6212,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6227,7 +6222,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6369,7 +6369,7 @@
         <v>133240767</v>
       </c>
       <c r="B53" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6478,10 +6478,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133240764</v>
+        <v>133240758</v>
       </c>
       <c r="B54" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>623736</v>
+        <v>623824</v>
       </c>
       <c r="R54" t="n">
-        <v>6942051</v>
+        <v>6941997</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6590,10 +6590,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133240758</v>
+        <v>133240764</v>
       </c>
       <c r="B55" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>623824</v>
+        <v>623736</v>
       </c>
       <c r="R55" t="n">
-        <v>6941997</v>
+        <v>6942051</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6702,10 +6702,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133240761</v>
+        <v>133240776</v>
       </c>
       <c r="B56" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>623740</v>
+        <v>623720</v>
       </c>
       <c r="R56" t="n">
-        <v>6942057</v>
+        <v>6941939</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>18 sex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6814,10 +6814,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133240776</v>
+        <v>133240761</v>
       </c>
       <c r="B57" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>623720</v>
+        <v>623740</v>
       </c>
       <c r="R57" t="n">
-        <v>6941939</v>
+        <v>6942057</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>18 sex</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6929,7 +6929,7 @@
         <v>133240754</v>
       </c>
       <c r="B58" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>133240759</v>
       </c>
       <c r="B59" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>133240777</v>
       </c>
       <c r="B60" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>133240756</v>
       </c>
       <c r="B61" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -4045,10 +4045,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133202437</v>
+        <v>133202440</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,42 +4056,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623840</v>
+        <v>623827</v>
       </c>
       <c r="R32" t="n">
-        <v>6942067</v>
+        <v>6942150</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4123,7 +4115,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4133,12 +4125,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,10 +4152,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133202440</v>
+        <v>133202437</v>
       </c>
       <c r="B33" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4176,34 +4163,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623827</v>
+        <v>623840</v>
       </c>
       <c r="R33" t="n">
-        <v>6942150</v>
+        <v>6942067</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4235,7 +4230,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4245,7 +4240,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4619,32 +4619,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133202430</v>
+        <v>133202431</v>
       </c>
       <c r="B37" t="n">
-        <v>80439</v>
+        <v>80468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4657,7 +4657,7 @@
         <v>623819</v>
       </c>
       <c r="R37" t="n">
-        <v>6942027</v>
+        <v>6942029</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,32 +4726,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133202434</v>
+        <v>133202430</v>
       </c>
       <c r="B38" t="n">
-        <v>99140</v>
+        <v>80439</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>623790</v>
+        <v>623819</v>
       </c>
       <c r="R38" t="n">
-        <v>6942049</v>
+        <v>6942027</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4806,12 +4806,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,32 +4833,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133202431</v>
+        <v>133202434</v>
       </c>
       <c r="B39" t="n">
-        <v>80468</v>
+        <v>99140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4873,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623819</v>
+        <v>623790</v>
       </c>
       <c r="R39" t="n">
-        <v>6942029</v>
+        <v>6942049</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4908,7 +4903,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4918,7 +4913,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -1006,53 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202450</v>
+        <v>133202459</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623712</v>
+        <v>623775</v>
       </c>
       <c r="R5" t="n">
-        <v>6941985</v>
+        <v>6941872</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,12 +1086,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,53 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202461</v>
+        <v>133202438</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623727</v>
+        <v>623820</v>
       </c>
       <c r="R6" t="n">
-        <v>6941870</v>
+        <v>6942117</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,12 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,45 +1230,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202459</v>
+        <v>133202450</v>
       </c>
       <c r="B7" t="n">
-        <v>99140</v>
+        <v>57958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623775</v>
+        <v>623712</v>
       </c>
       <c r="R7" t="n">
-        <v>6941872</v>
+        <v>6941985</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1318,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,45 +1350,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202438</v>
+        <v>133202461</v>
       </c>
       <c r="B8" t="n">
-        <v>99140</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623820</v>
+        <v>623727</v>
       </c>
       <c r="R8" t="n">
-        <v>6942117</v>
+        <v>6941870</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3366,32 +3366,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133202455</v>
+        <v>133202444</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>92348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6040186</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3401,13 +3401,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623779</v>
+        <v>623743</v>
       </c>
       <c r="R26" t="n">
-        <v>6941893</v>
+        <v>6942053</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,12 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>300+ ex</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,6 +3455,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3478,32 +3474,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133202444</v>
+        <v>133202455</v>
       </c>
       <c r="B27" t="n">
-        <v>92348</v>
+        <v>99140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6040186</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3513,13 +3509,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623743</v>
+        <v>623779</v>
       </c>
       <c r="R27" t="n">
-        <v>6942053</v>
+        <v>6941893</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3548,7 +3544,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3558,7 +3554,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>300+ ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3567,7 +3568,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -1006,45 +1006,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202459</v>
+        <v>133202450</v>
       </c>
       <c r="B5" t="n">
-        <v>99140</v>
+        <v>57958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623775</v>
+        <v>623712</v>
       </c>
       <c r="R5" t="n">
-        <v>6941872</v>
+        <v>6941985</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1094,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,45 +1126,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202438</v>
+        <v>133202461</v>
       </c>
       <c r="B6" t="n">
-        <v>99140</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623820</v>
+        <v>623727</v>
       </c>
       <c r="R6" t="n">
-        <v>6942117</v>
+        <v>6941870</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1188,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1214,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,53 +1246,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202450</v>
+        <v>133202459</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623712</v>
+        <v>623775</v>
       </c>
       <c r="R7" t="n">
-        <v>6941985</v>
+        <v>6941872</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,7 +1316,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,12 +1326,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,53 +1358,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202461</v>
+        <v>133202438</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623727</v>
+        <v>623820</v>
       </c>
       <c r="R8" t="n">
-        <v>6941870</v>
+        <v>6942117</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -5714,10 +5714,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133240766</v>
+        <v>133240763</v>
       </c>
       <c r="B47" t="n">
-        <v>92576</v>
+        <v>92388</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>483</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5749,13 +5749,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623736</v>
+        <v>623739</v>
       </c>
       <c r="R47" t="n">
-        <v>6942055</v>
+        <v>6942054</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5821,10 +5821,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133240763</v>
+        <v>133240766</v>
       </c>
       <c r="B48" t="n">
-        <v>92388</v>
+        <v>92576</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>483</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623739</v>
+        <v>623736</v>
       </c>
       <c r="R48" t="n">
-        <v>6942054</v>
+        <v>6942055</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -3366,32 +3366,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133202444</v>
+        <v>133202455</v>
       </c>
       <c r="B26" t="n">
-        <v>92348</v>
+        <v>99140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3401,13 +3401,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623743</v>
+        <v>623779</v>
       </c>
       <c r="R26" t="n">
-        <v>6942053</v>
+        <v>6941893</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3446,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>300+ ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,7 +3460,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3474,32 +3478,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133202455</v>
+        <v>133202444</v>
       </c>
       <c r="B27" t="n">
-        <v>99140</v>
+        <v>92348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6040186</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3509,13 +3513,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623779</v>
+        <v>623743</v>
       </c>
       <c r="R27" t="n">
-        <v>6941893</v>
+        <v>6942053</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3544,7 +3548,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3554,12 +3558,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>300+ ex</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3568,6 +3567,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -5714,10 +5714,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133240763</v>
+        <v>133240766</v>
       </c>
       <c r="B47" t="n">
-        <v>92388</v>
+        <v>92576</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>483</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5749,13 +5749,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623739</v>
+        <v>623736</v>
       </c>
       <c r="R47" t="n">
-        <v>6942054</v>
+        <v>6942055</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5821,10 +5821,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133240766</v>
+        <v>133240763</v>
       </c>
       <c r="B48" t="n">
-        <v>92576</v>
+        <v>92388</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623736</v>
+        <v>623739</v>
       </c>
       <c r="R48" t="n">
-        <v>6942055</v>
+        <v>6942054</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -3366,32 +3366,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133202455</v>
+        <v>133202444</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>92348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6040186</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3401,13 +3401,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623779</v>
+        <v>623743</v>
       </c>
       <c r="R26" t="n">
-        <v>6941893</v>
+        <v>6942053</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,12 +3446,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>300+ ex</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,6 +3455,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3478,32 +3474,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133202444</v>
+        <v>133202455</v>
       </c>
       <c r="B27" t="n">
-        <v>92348</v>
+        <v>99140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6040186</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3513,13 +3509,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623743</v>
+        <v>623779</v>
       </c>
       <c r="R27" t="n">
-        <v>6942053</v>
+        <v>6941893</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3548,7 +3544,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3558,7 +3554,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>300+ ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3567,7 +3568,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133202425</v>
       </c>
       <c r="B2" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133202433</v>
       </c>
       <c r="B3" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133202423</v>
+        <v>133202459</v>
       </c>
       <c r="B4" t="n">
-        <v>91891</v>
+        <v>99168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623825</v>
+        <v>623775</v>
       </c>
       <c r="R4" t="n">
-        <v>6941925</v>
+        <v>6941872</v>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1014,7 @@
         <v>133202450</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1134,7 @@
         <v>133202461</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,32 +1251,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202459</v>
+        <v>133202423</v>
       </c>
       <c r="B7" t="n">
-        <v>99140</v>
+        <v>91910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,13 +1286,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623775</v>
+        <v>623825</v>
       </c>
       <c r="R7" t="n">
-        <v>6941872</v>
+        <v>6941925</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,12 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,7 +1361,7 @@
         <v>133202438</v>
       </c>
       <c r="B8" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>133202446</v>
       </c>
       <c r="B9" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>133202427</v>
       </c>
       <c r="B10" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>133202465</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>133202429</v>
       </c>
       <c r="B12" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133202436</v>
+        <v>133202424</v>
       </c>
       <c r="B13" t="n">
-        <v>91928</v>
+        <v>98033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623821</v>
+        <v>623813</v>
       </c>
       <c r="R13" t="n">
-        <v>6942067</v>
+        <v>6941951</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,32 +2023,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133202424</v>
+        <v>133202426</v>
       </c>
       <c r="B14" t="n">
-        <v>98005</v>
+        <v>99168</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623813</v>
+        <v>623801</v>
       </c>
       <c r="R14" t="n">
-        <v>6941951</v>
+        <v>6941940</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2103,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133202426</v>
+        <v>133202443</v>
       </c>
       <c r="B15" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623801</v>
+        <v>623768</v>
       </c>
       <c r="R15" t="n">
-        <v>6941940</v>
+        <v>6942054</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2200,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,12 +2215,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,32 +2247,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133202443</v>
+        <v>133202436</v>
       </c>
       <c r="B16" t="n">
-        <v>99140</v>
+        <v>91947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2282,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623768</v>
+        <v>623821</v>
       </c>
       <c r="R16" t="n">
-        <v>6942054</v>
+        <v>6942067</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2312,7 +2317,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,12 +2327,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,32 +2354,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133202452</v>
+        <v>133202453</v>
       </c>
       <c r="B17" t="n">
-        <v>91928</v>
+        <v>99168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2389,13 +2389,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623775</v>
+        <v>623773</v>
       </c>
       <c r="R17" t="n">
-        <v>6941903</v>
+        <v>6941896</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2434,7 +2434,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2461,32 +2466,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133202453</v>
+        <v>133202452</v>
       </c>
       <c r="B18" t="n">
-        <v>99140</v>
+        <v>91947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2496,13 +2501,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623773</v>
+        <v>623775</v>
       </c>
       <c r="R18" t="n">
-        <v>6941896</v>
+        <v>6941903</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2531,7 +2536,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2541,12 +2546,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,7 +2576,7 @@
         <v>133202442</v>
       </c>
       <c r="B19" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133202454</v>
+        <v>133202458</v>
       </c>
       <c r="B20" t="n">
-        <v>92227</v>
+        <v>57965</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,34 +2696,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623773</v>
+        <v>623770</v>
       </c>
       <c r="R20" t="n">
-        <v>6941893</v>
+        <v>6941875</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2755,7 +2763,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2765,7 +2773,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133202432</v>
+        <v>133202454</v>
       </c>
       <c r="B21" t="n">
-        <v>91928</v>
+        <v>92218</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,21 +2816,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2827,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623820</v>
+        <v>623773</v>
       </c>
       <c r="R21" t="n">
-        <v>6942033</v>
+        <v>6941893</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2862,7 +2875,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2872,7 +2885,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,7 +2915,7 @@
         <v>133202460</v>
       </c>
       <c r="B22" t="n">
-        <v>92300</v>
+        <v>92291</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,10 +3019,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133202458</v>
+        <v>133202464</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,7 +3052,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3049,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623770</v>
+        <v>623782</v>
       </c>
       <c r="R23" t="n">
-        <v>6941875</v>
+        <v>6941914</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3084,7 +3097,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3094,12 +3107,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3126,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133202464</v>
+        <v>133202432</v>
       </c>
       <c r="B24" t="n">
-        <v>57958</v>
+        <v>91947</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,42 +3150,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623782</v>
+        <v>623820</v>
       </c>
       <c r="R24" t="n">
-        <v>6941914</v>
+        <v>6942033</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3204,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3214,12 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,10 +3246,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133202441</v>
+        <v>133202444</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>92339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3257,42 +3257,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623776</v>
+        <v>623743</v>
       </c>
       <c r="R25" t="n">
-        <v>6942117</v>
+        <v>6942053</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3324,7 +3316,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3326,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,6 +3335,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3366,10 +3354,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133202444</v>
+        <v>133202441</v>
       </c>
       <c r="B26" t="n">
-        <v>92348</v>
+        <v>57965</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3377,34 +3365,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623743</v>
+        <v>623776</v>
       </c>
       <c r="R26" t="n">
-        <v>6942053</v>
+        <v>6942117</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3436,7 +3432,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3446,7 +3442,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,7 +3456,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>133202455</v>
       </c>
       <c r="B27" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>133202451</v>
       </c>
       <c r="B28" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>133202463</v>
       </c>
       <c r="B29" t="n">
-        <v>92227</v>
+        <v>92218</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>133202448</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>133202447</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>133202440</v>
       </c>
       <c r="B32" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>133202437</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>133202445</v>
       </c>
       <c r="B34" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>133202435</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>133202456</v>
       </c>
       <c r="B36" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4619,32 +4619,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133202431</v>
+        <v>133202430</v>
       </c>
       <c r="B37" t="n">
-        <v>80468</v>
+        <v>80453</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4657,7 +4657,7 @@
         <v>623819</v>
       </c>
       <c r="R37" t="n">
-        <v>6942029</v>
+        <v>6942027</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4726,32 +4726,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133202430</v>
+        <v>133202434</v>
       </c>
       <c r="B38" t="n">
-        <v>80439</v>
+        <v>99168</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>623819</v>
+        <v>623790</v>
       </c>
       <c r="R38" t="n">
-        <v>6942027</v>
+        <v>6942049</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4806,7 +4806,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4833,32 +4838,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133202434</v>
+        <v>133202431</v>
       </c>
       <c r="B39" t="n">
-        <v>99140</v>
+        <v>80482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4868,10 +4873,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623790</v>
+        <v>623819</v>
       </c>
       <c r="R39" t="n">
-        <v>6942049</v>
+        <v>6942029</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4903,7 +4908,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4913,12 +4918,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4948,7 +4948,7 @@
         <v>133202439</v>
       </c>
       <c r="B40" t="n">
-        <v>92224</v>
+        <v>92215</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>133240775</v>
       </c>
       <c r="B41" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>133240757</v>
       </c>
       <c r="B42" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5276,32 +5276,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133240755</v>
+        <v>133240773</v>
       </c>
       <c r="B43" t="n">
-        <v>56522</v>
+        <v>99168</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623822</v>
+        <v>623688</v>
       </c>
       <c r="R43" t="n">
-        <v>6941942</v>
+        <v>6941982</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Spillning ( färskt)</t>
+          <t>27 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,32 +5388,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133240773</v>
+        <v>133240755</v>
       </c>
       <c r="B44" t="n">
-        <v>99140</v>
+        <v>56529</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623688</v>
+        <v>623822</v>
       </c>
       <c r="R44" t="n">
-        <v>6941982</v>
+        <v>6941942</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>27 ex</t>
+          <t>Spillning ( färskt)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5503,7 +5503,7 @@
         <v>133240774</v>
       </c>
       <c r="B45" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>133240762</v>
       </c>
       <c r="B46" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5714,10 +5714,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133240766</v>
+        <v>133240763</v>
       </c>
       <c r="B47" t="n">
-        <v>92576</v>
+        <v>92379</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>483</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5749,13 +5749,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623736</v>
+        <v>623739</v>
       </c>
       <c r="R47" t="n">
-        <v>6942055</v>
+        <v>6942054</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5821,10 +5821,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133240763</v>
+        <v>133240766</v>
       </c>
       <c r="B48" t="n">
-        <v>92388</v>
+        <v>92613</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,21 +5832,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>483</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5856,13 +5856,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623739</v>
+        <v>623736</v>
       </c>
       <c r="R48" t="n">
-        <v>6942054</v>
+        <v>6942055</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5931,7 +5931,7 @@
         <v>133240772</v>
       </c>
       <c r="B49" t="n">
-        <v>91942</v>
+        <v>91961</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6035,32 +6035,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133240760</v>
+        <v>133240771</v>
       </c>
       <c r="B50" t="n">
-        <v>91928</v>
+        <v>99168</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623830</v>
+        <v>623737</v>
       </c>
       <c r="R50" t="n">
-        <v>6942141</v>
+        <v>6942012</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6115,7 +6115,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6142,32 +6147,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133240771</v>
+        <v>133240760</v>
       </c>
       <c r="B51" t="n">
-        <v>99140</v>
+        <v>91947</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6177,10 +6182,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623737</v>
+        <v>623830</v>
       </c>
       <c r="R51" t="n">
-        <v>6942012</v>
+        <v>6942141</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6212,7 +6217,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6222,12 +6227,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6257,7 +6257,7 @@
         <v>133240778</v>
       </c>
       <c r="B52" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>133240767</v>
       </c>
       <c r="B53" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>133240758</v>
       </c>
       <c r="B54" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>133240764</v>
       </c>
       <c r="B55" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>133240776</v>
       </c>
       <c r="B56" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>133240761</v>
       </c>
       <c r="B57" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>133240754</v>
       </c>
       <c r="B58" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>133240759</v>
       </c>
       <c r="B59" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>133240777</v>
       </c>
       <c r="B60" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>133240756</v>
       </c>
       <c r="B61" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -3698,10 +3698,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133202463</v>
+        <v>133202448</v>
       </c>
       <c r="B29" t="n">
-        <v>92218</v>
+        <v>57965</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3709,34 +3709,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623712</v>
+        <v>623750</v>
       </c>
       <c r="R29" t="n">
-        <v>6941856</v>
+        <v>6941932</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3768,7 +3776,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3778,7 +3786,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3805,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133202448</v>
+        <v>133202463</v>
       </c>
       <c r="B30" t="n">
-        <v>57965</v>
+        <v>92218</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3816,42 +3829,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623750</v>
+        <v>623712</v>
       </c>
       <c r="R30" t="n">
-        <v>6941932</v>
+        <v>6941856</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3883,7 +3888,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3893,12 +3898,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -5055,7 +5055,7 @@
         <v>133240775</v>
       </c>
       <c r="B41" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>133240757</v>
       </c>
       <c r="B42" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>133240773</v>
       </c>
       <c r="B43" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>133240755</v>
       </c>
       <c r="B44" t="n">
-        <v>56529</v>
+        <v>56539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>133240774</v>
       </c>
       <c r="B45" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>133240762</v>
       </c>
       <c r="B46" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>133240763</v>
       </c>
       <c r="B47" t="n">
-        <v>92379</v>
+        <v>92389</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>133240766</v>
       </c>
       <c r="B48" t="n">
-        <v>92613</v>
+        <v>92623</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>133240772</v>
       </c>
       <c r="B49" t="n">
-        <v>91961</v>
+        <v>91971</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>133240771</v>
       </c>
       <c r="B50" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>133240760</v>
       </c>
       <c r="B51" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>133240778</v>
       </c>
       <c r="B52" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>133240767</v>
       </c>
       <c r="B53" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>133240758</v>
       </c>
       <c r="B54" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>133240764</v>
       </c>
       <c r="B55" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>133240776</v>
       </c>
       <c r="B56" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>133240761</v>
       </c>
       <c r="B57" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>133240754</v>
       </c>
       <c r="B58" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>133240759</v>
       </c>
       <c r="B59" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>133240777</v>
       </c>
       <c r="B60" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>133240756</v>
       </c>
       <c r="B61" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 15177-2026 artfynd.xlsx
+++ b/artfynd/A 15177-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133202425</v>
+        <v>133202439</v>
       </c>
       <c r="B2" t="n">
-        <v>99168</v>
+        <v>92242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623809</v>
+        <v>623830</v>
       </c>
       <c r="R2" t="n">
-        <v>6941943</v>
+        <v>6942098</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>45 ex</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133202433</v>
+        <v>133240774</v>
       </c>
       <c r="B3" t="n">
-        <v>99168</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623817</v>
+        <v>623690</v>
       </c>
       <c r="R3" t="n">
-        <v>6942024</v>
+        <v>6941978</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>9 ex</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133202459</v>
+        <v>133240766</v>
       </c>
       <c r="B4" t="n">
-        <v>99168</v>
+        <v>92640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623775</v>
+        <v>623736</v>
       </c>
       <c r="R4" t="n">
-        <v>6941872</v>
+        <v>6942055</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133202450</v>
+        <v>133202454</v>
       </c>
       <c r="B5" t="n">
-        <v>57965</v>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623712</v>
+        <v>623773</v>
       </c>
       <c r="R5" t="n">
-        <v>6941985</v>
+        <v>6941893</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133202461</v>
+        <v>133202463</v>
       </c>
       <c r="B6" t="n">
-        <v>57965</v>
+        <v>92245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,42 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623727</v>
+        <v>623712</v>
       </c>
       <c r="R6" t="n">
-        <v>6941870</v>
+        <v>6941856</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133202423</v>
+        <v>133202427</v>
       </c>
       <c r="B7" t="n">
-        <v>91910</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623825</v>
+        <v>623760</v>
       </c>
       <c r="R7" t="n">
-        <v>6941925</v>
+        <v>6941982</v>
       </c>
       <c r="S7" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133202438</v>
+        <v>133202429</v>
       </c>
       <c r="B8" t="n">
-        <v>99168</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623820</v>
+        <v>623803</v>
       </c>
       <c r="R8" t="n">
-        <v>6942117</v>
+        <v>6942012</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>15 ex</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133202446</v>
+        <v>133202432</v>
       </c>
       <c r="B9" t="n">
-        <v>99168</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623764</v>
+        <v>623820</v>
       </c>
       <c r="R9" t="n">
-        <v>6942028</v>
+        <v>6942033</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1540,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>60 ex</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133202427</v>
+        <v>133202436</v>
       </c>
       <c r="B10" t="n">
-        <v>91947</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623760</v>
+        <v>623821</v>
       </c>
       <c r="R10" t="n">
-        <v>6941982</v>
+        <v>6942067</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1652,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133202465</v>
+        <v>133202440</v>
       </c>
       <c r="B11" t="n">
-        <v>57965</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,42 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623786</v>
+        <v>623827</v>
       </c>
       <c r="R11" t="n">
-        <v>6941918</v>
+        <v>6942150</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1767,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,12 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133202429</v>
+        <v>133202452</v>
       </c>
       <c r="B12" t="n">
-        <v>91947</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623803</v>
+        <v>623775</v>
       </c>
       <c r="R12" t="n">
-        <v>6942012</v>
+        <v>6941903</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1879,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133202424</v>
+        <v>133202456</v>
       </c>
       <c r="B13" t="n">
-        <v>98033</v>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623813</v>
+        <v>623769</v>
       </c>
       <c r="R13" t="n">
-        <v>6941951</v>
+        <v>6941877</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1986,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133202426</v>
+        <v>133240760</v>
       </c>
       <c r="B14" t="n">
-        <v>99168</v>
+        <v>91974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2058,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623801</v>
+        <v>623830</v>
       </c>
       <c r="R14" t="n">
-        <v>6941940</v>
+        <v>6942141</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2093,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,12 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>25 ex</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133202443</v>
+        <v>133240762</v>
       </c>
       <c r="B15" t="n">
-        <v>99168</v>
+        <v>91974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623768</v>
+        <v>623738</v>
       </c>
       <c r="R15" t="n">
-        <v>6942054</v>
+        <v>6942055</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2205,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,12 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133202436</v>
+        <v>133240772</v>
       </c>
       <c r="B16" t="n">
-        <v>91947</v>
+        <v>91988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2282,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623821</v>
+        <v>623681</v>
       </c>
       <c r="R16" t="n">
-        <v>6942067</v>
+        <v>6942020</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2317,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2327,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133202453</v>
+        <v>133240763</v>
       </c>
       <c r="B17" t="n">
-        <v>99168</v>
+        <v>92406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2389,13 +2315,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623773</v>
+        <v>623739</v>
       </c>
       <c r="R17" t="n">
-        <v>6941896</v>
+        <v>6942054</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2434,12 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133202452</v>
+        <v>133202460</v>
       </c>
       <c r="B18" t="n">
-        <v>91947</v>
+        <v>92318</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623775</v>
+        <v>623768</v>
       </c>
       <c r="R18" t="n">
-        <v>6941903</v>
+        <v>6941880</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2536,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2546,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2573,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133202442</v>
+        <v>133202423</v>
       </c>
       <c r="B19" t="n">
-        <v>99168</v>
+        <v>91937</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,13 +2529,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623770</v>
+        <v>623825</v>
       </c>
       <c r="R19" t="n">
-        <v>6942069</v>
+        <v>6941925</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2643,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,12 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10 ex</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2685,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133202458</v>
+        <v>133202430</v>
       </c>
       <c r="B20" t="n">
-        <v>57965</v>
+        <v>80488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,42 +2612,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623770</v>
+        <v>623819</v>
       </c>
       <c r="R20" t="n">
-        <v>6941875</v>
+        <v>6942027</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2763,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2773,12 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133202454</v>
+        <v>133202431</v>
       </c>
       <c r="B21" t="n">
-        <v>92218</v>
+        <v>80493</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2840,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623773</v>
+        <v>623819</v>
       </c>
       <c r="R21" t="n">
-        <v>6941893</v>
+        <v>6942029</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2875,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2885,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,45 +2815,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133202460</v>
+        <v>133202435</v>
       </c>
       <c r="B22" t="n">
-        <v>92291</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623768</v>
+        <v>623795</v>
       </c>
       <c r="R22" t="n">
-        <v>6941880</v>
+        <v>6942074</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2982,7 +2893,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2992,7 +2903,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3019,10 +2935,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133202464</v>
+        <v>133202437</v>
       </c>
       <c r="B23" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,10 +2978,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623782</v>
+        <v>623840</v>
       </c>
       <c r="R23" t="n">
-        <v>6941914</v>
+        <v>6942067</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3097,7 +3013,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3107,7 +3023,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3139,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133202432</v>
+        <v>133202441</v>
       </c>
       <c r="B24" t="n">
-        <v>91947</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3150,34 +3066,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623820</v>
+        <v>623776</v>
       </c>
       <c r="R24" t="n">
-        <v>6942033</v>
+        <v>6942117</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3209,7 +3133,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3219,7 +3143,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133202444</v>
+        <v>133202445</v>
       </c>
       <c r="B25" t="n">
-        <v>92339</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3257,34 +3186,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623743</v>
+        <v>623745</v>
       </c>
       <c r="R25" t="n">
-        <v>6942053</v>
+        <v>6942050</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3316,7 +3253,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3326,7 +3263,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,7 +3277,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3354,10 +3295,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133202441</v>
+        <v>133202447</v>
       </c>
       <c r="B26" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,7 +3328,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3397,10 +3338,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623776</v>
+        <v>623682</v>
       </c>
       <c r="R26" t="n">
-        <v>6942117</v>
+        <v>6942015</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3432,7 +3373,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3442,12 +3383,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,48 +3415,56 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133202455</v>
+        <v>133202448</v>
       </c>
       <c r="B27" t="n">
-        <v>99168</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623779</v>
+        <v>623750</v>
       </c>
       <c r="R27" t="n">
-        <v>6941893</v>
+        <v>6941932</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3544,7 +3493,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3554,12 +3503,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>300+ ex</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,45 +3535,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133202451</v>
+        <v>133202450</v>
       </c>
       <c r="B28" t="n">
-        <v>99168</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>623703</v>
+        <v>623712</v>
       </c>
       <c r="R28" t="n">
-        <v>6941984</v>
+        <v>6941985</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3656,7 +3613,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3666,12 +3623,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>60 ex</t>
+          <t>Färska och äldre ringhack längs med hela stammen. Syns väl i kikaren.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3698,10 +3655,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133202448</v>
+        <v>133202458</v>
       </c>
       <c r="B29" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3731,7 +3688,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3741,10 +3698,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623750</v>
+        <v>623770</v>
       </c>
       <c r="R29" t="n">
-        <v>6941932</v>
+        <v>6941875</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3776,7 +3733,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3786,12 +3743,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,10 +3775,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133202463</v>
+        <v>133202461</v>
       </c>
       <c r="B30" t="n">
-        <v>92218</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,34 +3786,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623712</v>
+        <v>623727</v>
       </c>
       <c r="R30" t="n">
-        <v>6941856</v>
+        <v>6941870</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3888,7 +3853,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3898,7 +3863,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3925,10 +3895,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133202447</v>
+        <v>133202464</v>
       </c>
       <c r="B31" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3968,10 +3938,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>623682</v>
+        <v>623782</v>
       </c>
       <c r="R31" t="n">
-        <v>6942015</v>
+        <v>6941914</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4003,7 +3973,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4013,7 +3983,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4045,10 +4015,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133202440</v>
+        <v>133202465</v>
       </c>
       <c r="B32" t="n">
-        <v>91947</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,34 +4026,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623827</v>
+        <v>623786</v>
       </c>
       <c r="R32" t="n">
-        <v>6942150</v>
+        <v>6941918</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4115,7 +4093,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4125,7 +4103,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133202437</v>
+        <v>133240778</v>
       </c>
       <c r="B33" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,24 +4164,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623840</v>
+        <v>623723</v>
       </c>
       <c r="R33" t="n">
-        <v>6942067</v>
+        <v>6941914</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4230,7 +4205,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4240,12 +4215,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på Tall ( äldre exemplar)</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4272,10 +4247,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133202445</v>
+        <v>133240755</v>
       </c>
       <c r="B34" t="n">
-        <v>57965</v>
+        <v>56539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4283,42 +4258,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623745</v>
+        <v>623822</v>
       </c>
       <c r="R34" t="n">
-        <v>6942050</v>
+        <v>6941942</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4350,7 +4317,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4360,12 +4327,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Spillning ( färskt)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4392,53 +4359,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133202435</v>
+        <v>133202425</v>
       </c>
       <c r="B35" t="n">
-        <v>57965</v>
+        <v>99195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stavre, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623795</v>
+        <v>623809</v>
       </c>
       <c r="R35" t="n">
-        <v>6942074</v>
+        <v>6941943</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4470,7 +4429,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4480,12 +4439,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4512,32 +4471,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133202456</v>
+        <v>133202426</v>
       </c>
       <c r="B36" t="n">
-        <v>91947</v>
+        <v>99195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4547,10 +4506,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>623769</v>
+        <v>623801</v>
       </c>
       <c r="R36" t="n">
-        <v>6941877</v>
+        <v>6941940</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4582,7 +4541,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4592,7 +4551,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4619,32 +4583,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133202430</v>
+        <v>133202433</v>
       </c>
       <c r="B37" t="n">
-        <v>80453</v>
+        <v>99195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4654,10 +4618,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623819</v>
+        <v>623817</v>
       </c>
       <c r="R37" t="n">
-        <v>6942027</v>
+        <v>6942024</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4689,7 +4653,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4699,7 +4663,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4729,7 +4698,7 @@
         <v>133202434</v>
       </c>
       <c r="B38" t="n">
-        <v>99168</v>
+        <v>99195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4838,32 +4807,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133202431</v>
+        <v>133202438</v>
       </c>
       <c r="B39" t="n">
-        <v>80482</v>
+        <v>99195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4873,10 +4842,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623819</v>
+        <v>623820</v>
       </c>
       <c r="R39" t="n">
-        <v>6942029</v>
+        <v>6942117</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4908,7 +4877,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4918,7 +4887,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4945,32 +4919,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133202439</v>
+        <v>133202442</v>
       </c>
       <c r="B40" t="n">
-        <v>92215</v>
+        <v>99195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>73</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4980,10 +4954,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>623830</v>
+        <v>623770</v>
       </c>
       <c r="R40" t="n">
-        <v>6942098</v>
+        <v>6942069</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5015,7 +4989,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5025,7 +4999,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5052,10 +5031,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133240775</v>
+        <v>133202443</v>
       </c>
       <c r="B41" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5087,10 +5066,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>623715</v>
+        <v>623768</v>
       </c>
       <c r="R41" t="n">
-        <v>6941950</v>
+        <v>6942054</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5122,7 +5101,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5132,12 +5111,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>16 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5164,10 +5143,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133240757</v>
+        <v>133202446</v>
       </c>
       <c r="B42" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5199,10 +5178,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>623833</v>
+        <v>623764</v>
       </c>
       <c r="R42" t="n">
-        <v>6941994</v>
+        <v>6942028</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5234,7 +5213,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5244,12 +5223,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5276,10 +5255,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133240773</v>
+        <v>133202451</v>
       </c>
       <c r="B43" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5311,10 +5290,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623688</v>
+        <v>623703</v>
       </c>
       <c r="R43" t="n">
-        <v>6941982</v>
+        <v>6941984</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5346,7 +5325,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,12 +5335,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>27 ex</t>
+          <t>60 ex</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5388,32 +5367,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133240755</v>
+        <v>133202453</v>
       </c>
       <c r="B44" t="n">
-        <v>56539</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5423,13 +5402,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623822</v>
+        <v>623773</v>
       </c>
       <c r="R44" t="n">
-        <v>6941942</v>
+        <v>6941896</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5458,7 +5437,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5468,12 +5447,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Spillning ( färskt)</t>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5500,32 +5479,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133240774</v>
+        <v>133202455</v>
       </c>
       <c r="B45" t="n">
-        <v>79390</v>
+        <v>99195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5535,13 +5514,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>623690</v>
+        <v>623779</v>
       </c>
       <c r="R45" t="n">
-        <v>6941978</v>
+        <v>6941893</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5570,7 +5549,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5580,7 +5559,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>300+ ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5607,32 +5591,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133240762</v>
+        <v>133202459</v>
       </c>
       <c r="B46" t="n">
-        <v>91957</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5642,10 +5626,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>623738</v>
+        <v>623775</v>
       </c>
       <c r="R46" t="n">
-        <v>6942055</v>
+        <v>6941872</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5677,7 +5661,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5687,7 +5671,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5714,10 +5703,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133240763</v>
+        <v>133240754</v>
       </c>
       <c r="B47" t="n">
-        <v>92389</v>
+        <v>99195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,21 +5714,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5749,10 +5738,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623739</v>
+        <v>623822</v>
       </c>
       <c r="R47" t="n">
-        <v>6942054</v>
+        <v>6941942</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5784,7 +5773,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5794,7 +5783,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5821,10 +5815,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133240766</v>
+        <v>133240756</v>
       </c>
       <c r="B48" t="n">
-        <v>92623</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,21 +5826,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5856,13 +5850,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623736</v>
+        <v>623834</v>
       </c>
       <c r="R48" t="n">
-        <v>6942055</v>
+        <v>6941990</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5891,7 +5885,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5901,7 +5895,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>29 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5928,32 +5927,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133240772</v>
+        <v>133240757</v>
       </c>
       <c r="B49" t="n">
-        <v>91971</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5963,10 +5962,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623681</v>
+        <v>623833</v>
       </c>
       <c r="R49" t="n">
-        <v>6942020</v>
+        <v>6941994</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5998,7 +5997,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6008,7 +6007,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6035,10 +6039,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133240771</v>
+        <v>133240758</v>
       </c>
       <c r="B50" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6070,10 +6074,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623737</v>
+        <v>623824</v>
       </c>
       <c r="R50" t="n">
-        <v>6942012</v>
+        <v>6941997</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6105,7 +6109,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6115,12 +6119,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6147,32 +6151,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133240760</v>
+        <v>133240759</v>
       </c>
       <c r="B51" t="n">
-        <v>91957</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6182,10 +6186,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623830</v>
+        <v>623852</v>
       </c>
       <c r="R51" t="n">
-        <v>6942141</v>
+        <v>6942122</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6217,7 +6221,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6227,7 +6231,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6254,32 +6263,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133240778</v>
+        <v>133240761</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6289,10 +6298,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>623723</v>
+        <v>623740</v>
       </c>
       <c r="R52" t="n">
-        <v>6941914</v>
+        <v>6942057</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6324,7 +6333,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6334,12 +6343,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack på Tall ( äldre exemplar)</t>
+          <t>18 sex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6366,10 +6375,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133240767</v>
+        <v>133240764</v>
       </c>
       <c r="B53" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6401,10 +6410,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>623753</v>
+        <v>623736</v>
       </c>
       <c r="R53" t="n">
-        <v>6942055</v>
+        <v>6942051</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6436,7 +6445,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6446,12 +6455,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>57 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6478,10 +6487,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133240758</v>
+        <v>133240767</v>
       </c>
       <c r="B54" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6513,10 +6522,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>623824</v>
+        <v>623753</v>
       </c>
       <c r="R54" t="n">
-        <v>6941997</v>
+        <v>6942055</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6548,7 +6557,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6558,12 +6567,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>57 ex</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6590,10 +6599,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133240764</v>
+        <v>133240771</v>
       </c>
       <c r="B55" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6625,10 +6634,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>623736</v>
+        <v>623737</v>
       </c>
       <c r="R55" t="n">
-        <v>6942051</v>
+        <v>6942012</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6660,7 +6669,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6670,7 +6679,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6702,10 +6711,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133240776</v>
+        <v>133240773</v>
       </c>
       <c r="B56" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6737,10 +6746,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>623720</v>
+        <v>623688</v>
       </c>
       <c r="R56" t="n">
-        <v>6941939</v>
+        <v>6941982</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6772,7 +6781,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6782,12 +6791,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>27 ex</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6814,10 +6823,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133240761</v>
+        <v>133240775</v>
       </c>
       <c r="B57" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6849,10 +6858,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>623740</v>
+        <v>623715</v>
       </c>
       <c r="R57" t="n">
-        <v>6942057</v>
+        <v>6941950</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6884,7 +6893,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6894,12 +6903,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>18 sex</t>
+          <t>16 ex</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6926,10 +6935,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133240754</v>
+        <v>133240776</v>
       </c>
       <c r="B58" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6961,10 +6970,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>623822</v>
+        <v>623720</v>
       </c>
       <c r="R58" t="n">
-        <v>6941942</v>
+        <v>6941939</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6996,7 +7005,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7006,12 +7015,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7038,10 +7047,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133240759</v>
+        <v>133240777</v>
       </c>
       <c r="B59" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7073,10 +7082,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>623852</v>
+        <v>623724</v>
       </c>
       <c r="R59" t="n">
-        <v>6942122</v>
+        <v>6941914</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7108,7 +7117,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7118,12 +7127,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7150,32 +7159,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133240777</v>
+        <v>133202424</v>
       </c>
       <c r="B60" t="n">
-        <v>99178</v>
+        <v>98060</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7185,10 +7194,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>623724</v>
+        <v>623813</v>
       </c>
       <c r="R60" t="n">
-        <v>6941914</v>
+        <v>6941951</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7220,7 +7229,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7230,12 +7239,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>20 ex</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7262,32 +7266,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133240756</v>
+        <v>133202444</v>
       </c>
       <c r="B61" t="n">
-        <v>99178</v>
+        <v>92366</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6040186</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7297,10 +7301,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>623834</v>
+        <v>623743</v>
       </c>
       <c r="R61" t="n">
-        <v>6941990</v>
+        <v>6942053</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7332,7 +7336,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7342,12 +7346,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>29 ex</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7356,6 +7355,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
